--- a/test/owner200.xlsx
+++ b/test/owner200.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A155E4A0-1BF3-4192-B9F7-B147780A710F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C290309A-3B1E-483A-B5B2-DCB161221EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="1211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="1209">
   <si>
     <t>client_id</t>
   </si>
@@ -100,9 +100,6 @@
     <t>Devi</t>
   </si>
   <si>
-    <t>KLMN9012P</t>
-  </si>
-  <si>
     <t>dbenneton2@yellowpages.com</t>
   </si>
   <si>
@@ -119,9 +116,6 @@
   </si>
   <si>
     <t>Zabrina</t>
-  </si>
-  <si>
-    <t>FGHI5678J</t>
   </si>
   <si>
     <t>zboumphrey3@senate.gov</t>
@@ -4065,7 +4059,7 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -4103,7 +4097,7 @@
         <v>19</v>
       </c>
       <c r="C3">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -4144,7 +4138,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E4">
         <v>567890123456</v>
@@ -4153,22 +4147,22 @@
         <v>7412589630</v>
       </c>
       <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
         <v>28</v>
       </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>29</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>30</v>
-      </c>
-      <c r="L4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -4176,13 +4170,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E5">
         <v>123456789012</v>
@@ -4191,22 +4185,22 @@
         <v>7412589630</v>
       </c>
       <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
         <v>35</v>
       </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="L5" t="s">
         <v>36</v>
-      </c>
-      <c r="K5" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -4214,13 +4208,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6">
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>567890123456</v>
@@ -4229,22 +4223,22 @@
         <v>7412589630</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
       </c>
       <c r="J6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" t="s">
         <v>42</v>
-      </c>
-      <c r="K6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -4252,7 +4246,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -4267,22 +4261,22 @@
         <v>7890456123</v>
       </c>
       <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
         <v>46</v>
       </c>
-      <c r="H7" t="s">
+      <c r="K7" t="s">
         <v>47</v>
       </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="L7" t="s">
         <v>48</v>
-      </c>
-      <c r="K7" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -4290,13 +4284,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C8">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E8">
         <v>567890123456</v>
@@ -4305,22 +4299,22 @@
         <v>7412589630</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
       </c>
       <c r="J8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" t="s">
         <v>54</v>
-      </c>
-      <c r="K8" t="s">
-        <v>55</v>
-      </c>
-      <c r="L8" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -4328,13 +4322,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E9">
         <v>345678901234</v>
@@ -4343,22 +4337,22 @@
         <v>7412589630</v>
       </c>
       <c r="G9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
         <v>58</v>
       </c>
-      <c r="H9" t="s">
+      <c r="K9" t="s">
         <v>59</v>
       </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="L9" t="s">
         <v>60</v>
-      </c>
-      <c r="K9" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -4366,13 +4360,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E10">
         <v>123456789012</v>
@@ -4381,22 +4375,22 @@
         <v>3214569870</v>
       </c>
       <c r="G10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
         <v>64</v>
       </c>
-      <c r="H10" t="s">
+      <c r="K10" t="s">
         <v>65</v>
       </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="L10" t="s">
         <v>66</v>
-      </c>
-      <c r="K10" t="s">
-        <v>67</v>
-      </c>
-      <c r="L10" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -4404,13 +4398,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C11">
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E11">
         <v>345678901234</v>
@@ -4419,22 +4413,22 @@
         <v>7412589630</v>
       </c>
       <c r="G11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
         <v>70</v>
       </c>
-      <c r="H11" t="s">
+      <c r="K11" t="s">
         <v>71</v>
       </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="L11" t="s">
         <v>72</v>
-      </c>
-      <c r="K11" t="s">
-        <v>73</v>
-      </c>
-      <c r="L11" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -4442,13 +4436,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12">
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E12">
         <v>567890123456</v>
@@ -4457,22 +4451,22 @@
         <v>7890456123</v>
       </c>
       <c r="G12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
         <v>76</v>
       </c>
-      <c r="H12" t="s">
+      <c r="K12" t="s">
         <v>77</v>
       </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="L12" t="s">
         <v>78</v>
-      </c>
-      <c r="K12" t="s">
-        <v>79</v>
-      </c>
-      <c r="L12" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -4480,13 +4474,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E13">
         <v>123456789012</v>
@@ -4495,22 +4489,22 @@
         <v>7890456123</v>
       </c>
       <c r="G13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
         <v>82</v>
       </c>
-      <c r="H13" t="s">
+      <c r="K13" t="s">
         <v>83</v>
       </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="L13" t="s">
         <v>84</v>
-      </c>
-      <c r="K13" t="s">
-        <v>85</v>
-      </c>
-      <c r="L13" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -4518,13 +4512,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E14">
         <v>123456789012</v>
@@ -4533,22 +4527,22 @@
         <v>7412589630</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
       </c>
       <c r="J14" t="s">
+        <v>88</v>
+      </c>
+      <c r="K14" t="s">
+        <v>89</v>
+      </c>
+      <c r="L14" t="s">
         <v>90</v>
-      </c>
-      <c r="K14" t="s">
-        <v>91</v>
-      </c>
-      <c r="L14" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -4556,7 +4550,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -4571,22 +4565,22 @@
         <v>7890456123</v>
       </c>
       <c r="G15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
       </c>
       <c r="J15" t="s">
+        <v>94</v>
+      </c>
+      <c r="K15" t="s">
+        <v>95</v>
+      </c>
+      <c r="L15" t="s">
         <v>96</v>
-      </c>
-      <c r="K15" t="s">
-        <v>97</v>
-      </c>
-      <c r="L15" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
@@ -4594,13 +4588,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E16">
         <v>345678901234</v>
@@ -4609,22 +4603,22 @@
         <v>7890456123</v>
       </c>
       <c r="G16" t="s">
+        <v>98</v>
+      </c>
+      <c r="H16" t="s">
+        <v>99</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="s">
         <v>100</v>
       </c>
-      <c r="H16" t="s">
+      <c r="K16" t="s">
         <v>101</v>
       </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="L16" t="s">
         <v>102</v>
-      </c>
-      <c r="K16" t="s">
-        <v>103</v>
-      </c>
-      <c r="L16" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
@@ -4632,13 +4626,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E17">
         <v>567890123456</v>
@@ -4647,22 +4641,22 @@
         <v>7890456123</v>
       </c>
       <c r="G17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
       </c>
       <c r="J17" t="s">
+        <v>106</v>
+      </c>
+      <c r="K17" t="s">
+        <v>107</v>
+      </c>
+      <c r="L17" t="s">
         <v>108</v>
-      </c>
-      <c r="K17" t="s">
-        <v>109</v>
-      </c>
-      <c r="L17" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
@@ -4670,13 +4664,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C18">
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E18">
         <v>123456789012</v>
@@ -4685,22 +4679,22 @@
         <v>7412589630</v>
       </c>
       <c r="G18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
       </c>
       <c r="J18" t="s">
+        <v>112</v>
+      </c>
+      <c r="K18" t="s">
+        <v>113</v>
+      </c>
+      <c r="L18" t="s">
         <v>114</v>
-      </c>
-      <c r="K18" t="s">
-        <v>115</v>
-      </c>
-      <c r="L18" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
@@ -4708,13 +4702,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C19">
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E19">
         <v>123456789012</v>
@@ -4723,22 +4717,22 @@
         <v>7412589630</v>
       </c>
       <c r="G19" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19" t="s">
+        <v>117</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="s">
         <v>118</v>
       </c>
-      <c r="H19" t="s">
+      <c r="K19" t="s">
         <v>119</v>
       </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="L19" t="s">
         <v>120</v>
-      </c>
-      <c r="K19" t="s">
-        <v>121</v>
-      </c>
-      <c r="L19" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
@@ -4746,7 +4740,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C20">
         <v>5</v>
@@ -4761,22 +4755,22 @@
         <v>3214569870</v>
       </c>
       <c r="G20" t="s">
+        <v>122</v>
+      </c>
+      <c r="H20" t="s">
+        <v>123</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="s">
         <v>124</v>
       </c>
-      <c r="H20" t="s">
+      <c r="K20" t="s">
         <v>125</v>
       </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="L20" t="s">
         <v>126</v>
-      </c>
-      <c r="K20" t="s">
-        <v>127</v>
-      </c>
-      <c r="L20" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
@@ -4784,7 +4778,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -4799,22 +4793,22 @@
         <v>7412589630</v>
       </c>
       <c r="G21" t="s">
+        <v>128</v>
+      </c>
+      <c r="H21" t="s">
+        <v>129</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="s">
         <v>130</v>
       </c>
-      <c r="H21" t="s">
+      <c r="K21" t="s">
         <v>131</v>
       </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="L21" t="s">
         <v>132</v>
-      </c>
-      <c r="K21" t="s">
-        <v>133</v>
-      </c>
-      <c r="L21" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
@@ -4822,13 +4816,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E22">
         <v>345678901234</v>
@@ -4837,22 +4831,22 @@
         <v>7412589630</v>
       </c>
       <c r="G22" t="s">
+        <v>134</v>
+      </c>
+      <c r="H22" t="s">
+        <v>135</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="s">
         <v>136</v>
       </c>
-      <c r="H22" t="s">
+      <c r="K22" t="s">
         <v>137</v>
       </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="L22" t="s">
         <v>138</v>
-      </c>
-      <c r="K22" t="s">
-        <v>139</v>
-      </c>
-      <c r="L22" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
@@ -4860,13 +4854,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C23">
         <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E23">
         <v>123456789012</v>
@@ -4875,22 +4869,22 @@
         <v>7890456123</v>
       </c>
       <c r="G23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H23" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I23" t="b">
         <v>1</v>
       </c>
       <c r="J23" t="s">
+        <v>142</v>
+      </c>
+      <c r="K23" t="s">
+        <v>143</v>
+      </c>
+      <c r="L23" t="s">
         <v>144</v>
-      </c>
-      <c r="K23" t="s">
-        <v>145</v>
-      </c>
-      <c r="L23" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
@@ -4898,13 +4892,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E24">
         <v>567890123456</v>
@@ -4913,22 +4907,22 @@
         <v>3214569870</v>
       </c>
       <c r="G24" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H24" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I24" t="b">
         <v>1</v>
       </c>
       <c r="J24" t="s">
+        <v>148</v>
+      </c>
+      <c r="K24" t="s">
+        <v>149</v>
+      </c>
+      <c r="L24" t="s">
         <v>150</v>
-      </c>
-      <c r="K24" t="s">
-        <v>151</v>
-      </c>
-      <c r="L24" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
@@ -4936,13 +4930,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C25">
         <v>7</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E25">
         <v>345678901234</v>
@@ -4951,22 +4945,22 @@
         <v>7890456123</v>
       </c>
       <c r="G25" t="s">
+        <v>152</v>
+      </c>
+      <c r="H25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="s">
         <v>154</v>
       </c>
-      <c r="H25" t="s">
+      <c r="K25" t="s">
         <v>155</v>
       </c>
-      <c r="I25" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="L25" t="s">
         <v>156</v>
-      </c>
-      <c r="K25" t="s">
-        <v>157</v>
-      </c>
-      <c r="L25" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
@@ -4974,13 +4968,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C26">
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E26">
         <v>567890123456</v>
@@ -4989,22 +4983,22 @@
         <v>3214569870</v>
       </c>
       <c r="G26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H26" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I26" t="b">
         <v>1</v>
       </c>
       <c r="J26" t="s">
+        <v>160</v>
+      </c>
+      <c r="K26" t="s">
+        <v>161</v>
+      </c>
+      <c r="L26" t="s">
         <v>162</v>
-      </c>
-      <c r="K26" t="s">
-        <v>163</v>
-      </c>
-      <c r="L26" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
@@ -5012,7 +5006,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -5027,22 +5021,22 @@
         <v>3214569870</v>
       </c>
       <c r="G27" t="s">
+        <v>164</v>
+      </c>
+      <c r="H27" t="s">
+        <v>165</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="s">
         <v>166</v>
       </c>
-      <c r="H27" t="s">
+      <c r="K27" t="s">
         <v>167</v>
       </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J27" t="s">
+      <c r="L27" t="s">
         <v>168</v>
-      </c>
-      <c r="K27" t="s">
-        <v>169</v>
-      </c>
-      <c r="L27" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
@@ -5050,7 +5044,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -5065,22 +5059,22 @@
         <v>7890456123</v>
       </c>
       <c r="G28" t="s">
+        <v>170</v>
+      </c>
+      <c r="H28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="s">
         <v>172</v>
       </c>
-      <c r="H28" t="s">
+      <c r="K28" t="s">
         <v>173</v>
       </c>
-      <c r="I28" t="b">
-        <v>0</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="L28" t="s">
         <v>174</v>
-      </c>
-      <c r="K28" t="s">
-        <v>175</v>
-      </c>
-      <c r="L28" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
@@ -5088,13 +5082,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E29">
         <v>345678901234</v>
@@ -5103,22 +5097,22 @@
         <v>7890456123</v>
       </c>
       <c r="G29" t="s">
+        <v>176</v>
+      </c>
+      <c r="H29" t="s">
+        <v>177</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="s">
         <v>178</v>
       </c>
-      <c r="H29" t="s">
+      <c r="K29" t="s">
         <v>179</v>
       </c>
-      <c r="I29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J29" t="s">
+      <c r="L29" t="s">
         <v>180</v>
-      </c>
-      <c r="K29" t="s">
-        <v>181</v>
-      </c>
-      <c r="L29" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
@@ -5126,13 +5120,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E30">
         <v>567890123456</v>
@@ -5141,22 +5135,22 @@
         <v>3214569870</v>
       </c>
       <c r="G30" t="s">
+        <v>182</v>
+      </c>
+      <c r="H30" t="s">
+        <v>183</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="s">
         <v>184</v>
       </c>
-      <c r="H30" t="s">
+      <c r="K30" t="s">
         <v>185</v>
       </c>
-      <c r="I30" t="b">
-        <v>0</v>
-      </c>
-      <c r="J30" t="s">
+      <c r="L30" t="s">
         <v>186</v>
-      </c>
-      <c r="K30" t="s">
-        <v>187</v>
-      </c>
-      <c r="L30" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
@@ -5164,7 +5158,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C31">
         <v>7</v>
@@ -5179,22 +5173,22 @@
         <v>7890456123</v>
       </c>
       <c r="G31" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H31" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I31" t="b">
         <v>1</v>
       </c>
       <c r="J31" t="s">
+        <v>190</v>
+      </c>
+      <c r="K31" t="s">
+        <v>191</v>
+      </c>
+      <c r="L31" t="s">
         <v>192</v>
-      </c>
-      <c r="K31" t="s">
-        <v>193</v>
-      </c>
-      <c r="L31" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
@@ -5202,7 +5196,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C32">
         <v>8</v>
@@ -5217,22 +5211,22 @@
         <v>7890456123</v>
       </c>
       <c r="G32" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H32" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I32" t="b">
         <v>1</v>
       </c>
       <c r="J32" t="s">
+        <v>196</v>
+      </c>
+      <c r="K32" t="s">
+        <v>197</v>
+      </c>
+      <c r="L32" t="s">
         <v>198</v>
-      </c>
-      <c r="K32" t="s">
-        <v>199</v>
-      </c>
-      <c r="L32" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
@@ -5240,13 +5234,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E33">
         <v>123456789012</v>
@@ -5255,22 +5249,22 @@
         <v>7890456123</v>
       </c>
       <c r="G33" t="s">
+        <v>200</v>
+      </c>
+      <c r="H33" t="s">
+        <v>201</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="s">
         <v>202</v>
       </c>
-      <c r="H33" t="s">
+      <c r="K33" t="s">
         <v>203</v>
       </c>
-      <c r="I33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="L33" t="s">
         <v>204</v>
-      </c>
-      <c r="K33" t="s">
-        <v>205</v>
-      </c>
-      <c r="L33" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
@@ -5278,7 +5272,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -5293,22 +5287,22 @@
         <v>3214569870</v>
       </c>
       <c r="G34" t="s">
+        <v>206</v>
+      </c>
+      <c r="H34" t="s">
+        <v>207</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="s">
         <v>208</v>
       </c>
-      <c r="H34" t="s">
+      <c r="K34" t="s">
         <v>209</v>
       </c>
-      <c r="I34" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34" t="s">
+      <c r="L34" t="s">
         <v>210</v>
-      </c>
-      <c r="K34" t="s">
-        <v>211</v>
-      </c>
-      <c r="L34" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
@@ -5316,7 +5310,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C35">
         <v>5</v>
@@ -5331,22 +5325,22 @@
         <v>7412589630</v>
       </c>
       <c r="G35" t="s">
+        <v>212</v>
+      </c>
+      <c r="H35" t="s">
+        <v>213</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="s">
         <v>214</v>
       </c>
-      <c r="H35" t="s">
+      <c r="K35" t="s">
         <v>215</v>
       </c>
-      <c r="I35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" t="s">
+      <c r="L35" t="s">
         <v>216</v>
-      </c>
-      <c r="K35" t="s">
-        <v>217</v>
-      </c>
-      <c r="L35" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
@@ -5354,7 +5348,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C36">
         <v>7</v>
@@ -5369,22 +5363,22 @@
         <v>7412589630</v>
       </c>
       <c r="G36" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H36" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I36" t="b">
         <v>1</v>
       </c>
       <c r="J36" t="s">
+        <v>220</v>
+      </c>
+      <c r="K36" t="s">
+        <v>221</v>
+      </c>
+      <c r="L36" t="s">
         <v>222</v>
-      </c>
-      <c r="K36" t="s">
-        <v>223</v>
-      </c>
-      <c r="L36" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
@@ -5392,7 +5386,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C37">
         <v>8</v>
@@ -5407,22 +5401,22 @@
         <v>7890456123</v>
       </c>
       <c r="G37" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H37" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I37" t="b">
         <v>1</v>
       </c>
       <c r="J37" t="s">
+        <v>226</v>
+      </c>
+      <c r="K37" t="s">
+        <v>227</v>
+      </c>
+      <c r="L37" t="s">
         <v>228</v>
-      </c>
-      <c r="K37" t="s">
-        <v>229</v>
-      </c>
-      <c r="L37" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
@@ -5430,7 +5424,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C38">
         <v>7</v>
@@ -5445,22 +5439,22 @@
         <v>3214569870</v>
       </c>
       <c r="G38" t="s">
+        <v>230</v>
+      </c>
+      <c r="H38" t="s">
+        <v>231</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="s">
         <v>232</v>
       </c>
-      <c r="H38" t="s">
+      <c r="K38" t="s">
         <v>233</v>
       </c>
-      <c r="I38" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38" t="s">
+      <c r="L38" t="s">
         <v>234</v>
-      </c>
-      <c r="K38" t="s">
-        <v>235</v>
-      </c>
-      <c r="L38" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
@@ -5468,7 +5462,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C39">
         <v>6</v>
@@ -5483,22 +5477,22 @@
         <v>7890456123</v>
       </c>
       <c r="G39" t="s">
+        <v>236</v>
+      </c>
+      <c r="H39" t="s">
+        <v>237</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="s">
         <v>238</v>
       </c>
-      <c r="H39" t="s">
+      <c r="K39" t="s">
         <v>239</v>
       </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="L39" t="s">
         <v>240</v>
-      </c>
-      <c r="K39" t="s">
-        <v>241</v>
-      </c>
-      <c r="L39" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
@@ -5506,13 +5500,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C40">
         <v>7</v>
       </c>
       <c r="D40" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E40">
         <v>123456789012</v>
@@ -5521,22 +5515,22 @@
         <v>7412589630</v>
       </c>
       <c r="G40" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H40" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I40" t="b">
         <v>1</v>
       </c>
       <c r="J40" t="s">
+        <v>244</v>
+      </c>
+      <c r="K40" t="s">
+        <v>245</v>
+      </c>
+      <c r="L40" t="s">
         <v>246</v>
-      </c>
-      <c r="K40" t="s">
-        <v>247</v>
-      </c>
-      <c r="L40" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
@@ -5544,7 +5538,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C41">
         <v>4</v>
@@ -5559,22 +5553,22 @@
         <v>3214569870</v>
       </c>
       <c r="G41" t="s">
+        <v>248</v>
+      </c>
+      <c r="H41" t="s">
+        <v>249</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="s">
         <v>250</v>
       </c>
-      <c r="H41" t="s">
+      <c r="K41" t="s">
         <v>251</v>
       </c>
-      <c r="I41" t="b">
-        <v>0</v>
-      </c>
-      <c r="J41" t="s">
+      <c r="L41" t="s">
         <v>252</v>
-      </c>
-      <c r="K41" t="s">
-        <v>253</v>
-      </c>
-      <c r="L41" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
@@ -5582,13 +5576,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C42">
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E42">
         <v>123456789012</v>
@@ -5597,22 +5591,22 @@
         <v>7890456123</v>
       </c>
       <c r="G42" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H42" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I42" t="b">
         <v>1</v>
       </c>
       <c r="J42" t="s">
+        <v>256</v>
+      </c>
+      <c r="K42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L42" t="s">
         <v>258</v>
-      </c>
-      <c r="K42" t="s">
-        <v>259</v>
-      </c>
-      <c r="L42" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
@@ -5620,13 +5614,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E43">
         <v>123456789012</v>
@@ -5635,22 +5629,22 @@
         <v>3214569870</v>
       </c>
       <c r="G43" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I43" t="b">
         <v>1</v>
       </c>
       <c r="J43" t="s">
+        <v>262</v>
+      </c>
+      <c r="K43" t="s">
+        <v>263</v>
+      </c>
+      <c r="L43" t="s">
         <v>264</v>
-      </c>
-      <c r="K43" t="s">
-        <v>265</v>
-      </c>
-      <c r="L43" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
@@ -5658,13 +5652,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C44">
         <v>7</v>
       </c>
       <c r="D44" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E44">
         <v>123456789012</v>
@@ -5673,22 +5667,22 @@
         <v>7412589630</v>
       </c>
       <c r="G44" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H44" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I44" t="b">
         <v>1</v>
       </c>
       <c r="J44" t="s">
+        <v>268</v>
+      </c>
+      <c r="K44" t="s">
+        <v>269</v>
+      </c>
+      <c r="L44" t="s">
         <v>270</v>
-      </c>
-      <c r="K44" t="s">
-        <v>271</v>
-      </c>
-      <c r="L44" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
@@ -5696,13 +5690,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
       <c r="D45" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E45">
         <v>567890123456</v>
@@ -5711,22 +5705,22 @@
         <v>3214569870</v>
       </c>
       <c r="G45" t="s">
+        <v>272</v>
+      </c>
+      <c r="H45" t="s">
+        <v>273</v>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="s">
         <v>274</v>
       </c>
-      <c r="H45" t="s">
+      <c r="K45" t="s">
         <v>275</v>
       </c>
-      <c r="I45" t="b">
-        <v>0</v>
-      </c>
-      <c r="J45" t="s">
+      <c r="L45" t="s">
         <v>276</v>
-      </c>
-      <c r="K45" t="s">
-        <v>277</v>
-      </c>
-      <c r="L45" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
@@ -5734,7 +5728,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -5749,22 +5743,22 @@
         <v>3214569870</v>
       </c>
       <c r="G46" t="s">
+        <v>278</v>
+      </c>
+      <c r="H46" t="s">
+        <v>279</v>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="s">
         <v>280</v>
       </c>
-      <c r="H46" t="s">
+      <c r="K46" t="s">
         <v>281</v>
       </c>
-      <c r="I46" t="b">
-        <v>0</v>
-      </c>
-      <c r="J46" t="s">
+      <c r="L46" t="s">
         <v>282</v>
-      </c>
-      <c r="K46" t="s">
-        <v>283</v>
-      </c>
-      <c r="L46" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
@@ -5772,7 +5766,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C47">
         <v>5</v>
@@ -5787,22 +5781,22 @@
         <v>3214569870</v>
       </c>
       <c r="G47" t="s">
+        <v>283</v>
+      </c>
+      <c r="H47" t="s">
+        <v>284</v>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="s">
         <v>285</v>
       </c>
-      <c r="H47" t="s">
+      <c r="K47" t="s">
         <v>286</v>
       </c>
-      <c r="I47" t="b">
-        <v>0</v>
-      </c>
-      <c r="J47" t="s">
+      <c r="L47" t="s">
         <v>287</v>
-      </c>
-      <c r="K47" t="s">
-        <v>288</v>
-      </c>
-      <c r="L47" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
@@ -5810,13 +5804,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C48">
         <v>2</v>
       </c>
       <c r="D48" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E48">
         <v>123456789012</v>
@@ -5825,22 +5819,22 @@
         <v>3214569870</v>
       </c>
       <c r="G48" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H48" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I48" t="b">
         <v>1</v>
       </c>
       <c r="J48" t="s">
+        <v>291</v>
+      </c>
+      <c r="K48" t="s">
+        <v>292</v>
+      </c>
+      <c r="L48" t="s">
         <v>293</v>
-      </c>
-      <c r="K48" t="s">
-        <v>294</v>
-      </c>
-      <c r="L48" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
@@ -5848,13 +5842,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E49">
         <v>567890123456</v>
@@ -5863,22 +5857,22 @@
         <v>7890456123</v>
       </c>
       <c r="G49" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H49" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I49" t="b">
         <v>1</v>
       </c>
       <c r="J49" t="s">
+        <v>297</v>
+      </c>
+      <c r="K49" t="s">
+        <v>298</v>
+      </c>
+      <c r="L49" t="s">
         <v>299</v>
-      </c>
-      <c r="K49" t="s">
-        <v>300</v>
-      </c>
-      <c r="L49" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
@@ -5886,13 +5880,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E50">
         <v>123456789012</v>
@@ -5901,22 +5895,22 @@
         <v>7412589630</v>
       </c>
       <c r="G50" t="s">
+        <v>301</v>
+      </c>
+      <c r="H50" t="s">
+        <v>302</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="s">
         <v>303</v>
       </c>
-      <c r="H50" t="s">
+      <c r="K50" t="s">
         <v>304</v>
       </c>
-      <c r="I50" t="b">
-        <v>0</v>
-      </c>
-      <c r="J50" t="s">
+      <c r="L50" t="s">
         <v>305</v>
-      </c>
-      <c r="K50" t="s">
-        <v>306</v>
-      </c>
-      <c r="L50" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
@@ -5924,13 +5918,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E51">
         <v>123456789012</v>
@@ -5939,22 +5933,22 @@
         <v>3214569870</v>
       </c>
       <c r="G51" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H51" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I51" t="b">
         <v>1</v>
       </c>
       <c r="J51" t="s">
+        <v>309</v>
+      </c>
+      <c r="K51" t="s">
+        <v>310</v>
+      </c>
+      <c r="L51" t="s">
         <v>311</v>
-      </c>
-      <c r="K51" t="s">
-        <v>312</v>
-      </c>
-      <c r="L51" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
@@ -5962,7 +5956,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C52">
         <v>9</v>
@@ -5977,22 +5971,22 @@
         <v>7412589630</v>
       </c>
       <c r="G52" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H52" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
       </c>
       <c r="J52" t="s">
+        <v>315</v>
+      </c>
+      <c r="K52" t="s">
+        <v>316</v>
+      </c>
+      <c r="L52" t="s">
         <v>317</v>
-      </c>
-      <c r="K52" t="s">
-        <v>318</v>
-      </c>
-      <c r="L52" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
@@ -6000,13 +5994,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C53">
         <v>7</v>
       </c>
       <c r="D53" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E53">
         <v>123456789012</v>
@@ -6015,22 +6009,22 @@
         <v>7890456123</v>
       </c>
       <c r="G53" t="s">
+        <v>319</v>
+      </c>
+      <c r="H53" t="s">
+        <v>320</v>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="s">
         <v>321</v>
       </c>
-      <c r="H53" t="s">
+      <c r="K53" t="s">
         <v>322</v>
       </c>
-      <c r="I53" t="b">
-        <v>0</v>
-      </c>
-      <c r="J53" t="s">
+      <c r="L53" t="s">
         <v>323</v>
-      </c>
-      <c r="K53" t="s">
-        <v>324</v>
-      </c>
-      <c r="L53" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
@@ -6038,13 +6032,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C54">
         <v>2</v>
       </c>
       <c r="D54" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E54">
         <v>567890123456</v>
@@ -6053,22 +6047,22 @@
         <v>7890456123</v>
       </c>
       <c r="G54" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H54" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I54" t="b">
         <v>1</v>
       </c>
       <c r="J54" t="s">
+        <v>327</v>
+      </c>
+      <c r="K54" t="s">
+        <v>328</v>
+      </c>
+      <c r="L54" t="s">
         <v>329</v>
-      </c>
-      <c r="K54" t="s">
-        <v>330</v>
-      </c>
-      <c r="L54" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
@@ -6076,13 +6070,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C55">
         <v>6</v>
       </c>
       <c r="D55" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E55">
         <v>345678901234</v>
@@ -6091,22 +6085,22 @@
         <v>7412589630</v>
       </c>
       <c r="G55" t="s">
+        <v>331</v>
+      </c>
+      <c r="H55" t="s">
+        <v>332</v>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="s">
         <v>333</v>
       </c>
-      <c r="H55" t="s">
+      <c r="K55" t="s">
         <v>334</v>
       </c>
-      <c r="I55" t="b">
-        <v>0</v>
-      </c>
-      <c r="J55" t="s">
+      <c r="L55" t="s">
         <v>335</v>
-      </c>
-      <c r="K55" t="s">
-        <v>336</v>
-      </c>
-      <c r="L55" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
@@ -6114,7 +6108,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C56">
         <v>4</v>
@@ -6129,22 +6123,22 @@
         <v>7890456123</v>
       </c>
       <c r="G56" t="s">
+        <v>337</v>
+      </c>
+      <c r="H56" t="s">
+        <v>338</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="s">
         <v>339</v>
       </c>
-      <c r="H56" t="s">
+      <c r="K56" t="s">
         <v>340</v>
       </c>
-      <c r="I56" t="b">
-        <v>0</v>
-      </c>
-      <c r="J56" t="s">
+      <c r="L56" t="s">
         <v>341</v>
-      </c>
-      <c r="K56" t="s">
-        <v>342</v>
-      </c>
-      <c r="L56" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
@@ -6152,13 +6146,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C57">
         <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E57">
         <v>123456789012</v>
@@ -6167,22 +6161,22 @@
         <v>3214569870</v>
       </c>
       <c r="G57" t="s">
+        <v>343</v>
+      </c>
+      <c r="H57" t="s">
+        <v>344</v>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="s">
         <v>345</v>
       </c>
-      <c r="H57" t="s">
+      <c r="K57" t="s">
         <v>346</v>
       </c>
-      <c r="I57" t="b">
-        <v>0</v>
-      </c>
-      <c r="J57" t="s">
+      <c r="L57" t="s">
         <v>347</v>
-      </c>
-      <c r="K57" t="s">
-        <v>348</v>
-      </c>
-      <c r="L57" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
@@ -6190,13 +6184,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E58">
         <v>567890123456</v>
@@ -6205,22 +6199,22 @@
         <v>7890456123</v>
       </c>
       <c r="G58" t="s">
+        <v>349</v>
+      </c>
+      <c r="H58" t="s">
+        <v>350</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="s">
         <v>351</v>
       </c>
-      <c r="H58" t="s">
+      <c r="K58" t="s">
         <v>352</v>
       </c>
-      <c r="I58" t="b">
-        <v>0</v>
-      </c>
-      <c r="J58" t="s">
+      <c r="L58" t="s">
         <v>353</v>
-      </c>
-      <c r="K58" t="s">
-        <v>354</v>
-      </c>
-      <c r="L58" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
@@ -6228,7 +6222,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -6243,22 +6237,22 @@
         <v>7890456123</v>
       </c>
       <c r="G59" t="s">
+        <v>355</v>
+      </c>
+      <c r="H59" t="s">
+        <v>356</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" t="s">
         <v>357</v>
       </c>
-      <c r="H59" t="s">
+      <c r="K59" t="s">
         <v>358</v>
       </c>
-      <c r="I59" t="b">
-        <v>0</v>
-      </c>
-      <c r="J59" t="s">
+      <c r="L59" t="s">
         <v>359</v>
-      </c>
-      <c r="K59" t="s">
-        <v>360</v>
-      </c>
-      <c r="L59" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
@@ -6266,7 +6260,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C60">
         <v>3</v>
@@ -6281,22 +6275,22 @@
         <v>7412589630</v>
       </c>
       <c r="G60" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H60" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="I60" t="b">
         <v>1</v>
       </c>
       <c r="J60" t="s">
+        <v>363</v>
+      </c>
+      <c r="K60" t="s">
+        <v>364</v>
+      </c>
+      <c r="L60" t="s">
         <v>365</v>
-      </c>
-      <c r="K60" t="s">
-        <v>366</v>
-      </c>
-      <c r="L60" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
@@ -6304,13 +6298,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C61">
         <v>5</v>
       </c>
       <c r="D61" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E61">
         <v>345678901234</v>
@@ -6319,22 +6313,22 @@
         <v>3214569870</v>
       </c>
       <c r="G61" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H61" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I61" t="b">
         <v>1</v>
       </c>
       <c r="J61" t="s">
+        <v>369</v>
+      </c>
+      <c r="K61" t="s">
+        <v>370</v>
+      </c>
+      <c r="L61" t="s">
         <v>371</v>
-      </c>
-      <c r="K61" t="s">
-        <v>372</v>
-      </c>
-      <c r="L61" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
@@ -6342,13 +6336,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E62">
         <v>123456789012</v>
@@ -6357,22 +6351,22 @@
         <v>7412589630</v>
       </c>
       <c r="G62" t="s">
+        <v>373</v>
+      </c>
+      <c r="H62" t="s">
+        <v>374</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62" t="s">
         <v>375</v>
       </c>
-      <c r="H62" t="s">
+      <c r="K62" t="s">
         <v>376</v>
       </c>
-      <c r="I62" t="b">
-        <v>0</v>
-      </c>
-      <c r="J62" t="s">
+      <c r="L62" t="s">
         <v>377</v>
-      </c>
-      <c r="K62" t="s">
-        <v>378</v>
-      </c>
-      <c r="L62" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
@@ -6380,13 +6374,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C63">
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E63">
         <v>567890123456</v>
@@ -6395,22 +6389,22 @@
         <v>3214569870</v>
       </c>
       <c r="G63" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H63" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I63" t="b">
         <v>1</v>
       </c>
       <c r="J63" t="s">
+        <v>381</v>
+      </c>
+      <c r="K63" t="s">
+        <v>382</v>
+      </c>
+      <c r="L63" t="s">
         <v>383</v>
-      </c>
-      <c r="K63" t="s">
-        <v>384</v>
-      </c>
-      <c r="L63" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
@@ -6418,13 +6412,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C64">
         <v>7</v>
       </c>
       <c r="D64" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E64">
         <v>123456789012</v>
@@ -6433,22 +6427,22 @@
         <v>7412589630</v>
       </c>
       <c r="G64" t="s">
+        <v>385</v>
+      </c>
+      <c r="H64" t="s">
+        <v>386</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" t="s">
         <v>387</v>
       </c>
-      <c r="H64" t="s">
+      <c r="K64" t="s">
         <v>388</v>
       </c>
-      <c r="I64" t="b">
-        <v>0</v>
-      </c>
-      <c r="J64" t="s">
+      <c r="L64" t="s">
         <v>389</v>
-      </c>
-      <c r="K64" t="s">
-        <v>390</v>
-      </c>
-      <c r="L64" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
@@ -6456,13 +6450,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C65">
         <v>5</v>
       </c>
       <c r="D65" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E65">
         <v>123456789012</v>
@@ -6471,22 +6465,22 @@
         <v>7890456123</v>
       </c>
       <c r="G65" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H65" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I65" t="b">
         <v>1</v>
       </c>
       <c r="J65" t="s">
+        <v>393</v>
+      </c>
+      <c r="K65" t="s">
+        <v>394</v>
+      </c>
+      <c r="L65" t="s">
         <v>395</v>
-      </c>
-      <c r="K65" t="s">
-        <v>396</v>
-      </c>
-      <c r="L65" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
@@ -6494,13 +6488,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C66">
         <v>7</v>
       </c>
       <c r="D66" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E66">
         <v>345678901234</v>
@@ -6509,22 +6503,22 @@
         <v>3214569870</v>
       </c>
       <c r="G66" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H66" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I66" t="b">
         <v>1</v>
       </c>
       <c r="J66" t="s">
+        <v>399</v>
+      </c>
+      <c r="K66" t="s">
+        <v>400</v>
+      </c>
+      <c r="L66" t="s">
         <v>401</v>
-      </c>
-      <c r="K66" t="s">
-        <v>402</v>
-      </c>
-      <c r="L66" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
@@ -6532,13 +6526,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C67">
         <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E67">
         <v>345678901234</v>
@@ -6547,22 +6541,22 @@
         <v>3214569870</v>
       </c>
       <c r="G67" t="s">
+        <v>403</v>
+      </c>
+      <c r="H67" t="s">
+        <v>404</v>
+      </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67" t="s">
         <v>405</v>
       </c>
-      <c r="H67" t="s">
+      <c r="K67" t="s">
         <v>406</v>
       </c>
-      <c r="I67" t="b">
-        <v>0</v>
-      </c>
-      <c r="J67" t="s">
+      <c r="L67" t="s">
         <v>407</v>
-      </c>
-      <c r="K67" t="s">
-        <v>408</v>
-      </c>
-      <c r="L67" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
@@ -6570,13 +6564,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C68">
         <v>8</v>
       </c>
       <c r="D68" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E68">
         <v>567890123456</v>
@@ -6585,22 +6579,22 @@
         <v>7412589630</v>
       </c>
       <c r="G68" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H68" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I68" t="b">
         <v>1</v>
       </c>
       <c r="J68" t="s">
+        <v>411</v>
+      </c>
+      <c r="K68" t="s">
+        <v>412</v>
+      </c>
+      <c r="L68" t="s">
         <v>413</v>
-      </c>
-      <c r="K68" t="s">
-        <v>414</v>
-      </c>
-      <c r="L68" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
@@ -6608,13 +6602,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E69">
         <v>567890123456</v>
@@ -6623,22 +6617,22 @@
         <v>3214569870</v>
       </c>
       <c r="G69" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H69" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I69" t="b">
         <v>1</v>
       </c>
       <c r="J69" t="s">
+        <v>417</v>
+      </c>
+      <c r="K69" t="s">
+        <v>418</v>
+      </c>
+      <c r="L69" t="s">
         <v>419</v>
-      </c>
-      <c r="K69" t="s">
-        <v>420</v>
-      </c>
-      <c r="L69" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
@@ -6646,7 +6640,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C70">
         <v>9</v>
@@ -6661,22 +6655,22 @@
         <v>3214569870</v>
       </c>
       <c r="G70" t="s">
+        <v>421</v>
+      </c>
+      <c r="H70" t="s">
+        <v>422</v>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70" t="s">
         <v>423</v>
       </c>
-      <c r="H70" t="s">
+      <c r="K70" t="s">
         <v>424</v>
       </c>
-      <c r="I70" t="b">
-        <v>0</v>
-      </c>
-      <c r="J70" t="s">
+      <c r="L70" t="s">
         <v>425</v>
-      </c>
-      <c r="K70" t="s">
-        <v>426</v>
-      </c>
-      <c r="L70" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
@@ -6684,13 +6678,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C71">
         <v>7</v>
       </c>
       <c r="D71" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E71">
         <v>567890123456</v>
@@ -6699,22 +6693,22 @@
         <v>3214569870</v>
       </c>
       <c r="G71" t="s">
+        <v>427</v>
+      </c>
+      <c r="H71" t="s">
+        <v>428</v>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71" t="s">
         <v>429</v>
       </c>
-      <c r="H71" t="s">
+      <c r="K71" t="s">
         <v>430</v>
       </c>
-      <c r="I71" t="b">
-        <v>0</v>
-      </c>
-      <c r="J71" t="s">
+      <c r="L71" t="s">
         <v>431</v>
-      </c>
-      <c r="K71" t="s">
-        <v>432</v>
-      </c>
-      <c r="L71" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
@@ -6722,13 +6716,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C72">
         <v>9</v>
       </c>
       <c r="D72" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E72">
         <v>123456789012</v>
@@ -6737,22 +6731,22 @@
         <v>7412589630</v>
       </c>
       <c r="G72" t="s">
+        <v>433</v>
+      </c>
+      <c r="H72" t="s">
+        <v>434</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72" t="s">
         <v>435</v>
       </c>
-      <c r="H72" t="s">
+      <c r="K72" t="s">
         <v>436</v>
       </c>
-      <c r="I72" t="b">
-        <v>0</v>
-      </c>
-      <c r="J72" t="s">
+      <c r="L72" t="s">
         <v>437</v>
-      </c>
-      <c r="K72" t="s">
-        <v>438</v>
-      </c>
-      <c r="L72" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
@@ -6760,13 +6754,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C73">
         <v>1</v>
       </c>
       <c r="D73" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E73">
         <v>567890123456</v>
@@ -6775,22 +6769,22 @@
         <v>3214569870</v>
       </c>
       <c r="G73" t="s">
+        <v>439</v>
+      </c>
+      <c r="H73" t="s">
+        <v>440</v>
+      </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" t="s">
         <v>441</v>
       </c>
-      <c r="H73" t="s">
+      <c r="K73" t="s">
         <v>442</v>
       </c>
-      <c r="I73" t="b">
-        <v>0</v>
-      </c>
-      <c r="J73" t="s">
+      <c r="L73" t="s">
         <v>443</v>
-      </c>
-      <c r="K73" t="s">
-        <v>444</v>
-      </c>
-      <c r="L73" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
@@ -6798,7 +6792,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C74">
         <v>3</v>
@@ -6813,22 +6807,22 @@
         <v>7412589630</v>
       </c>
       <c r="G74" t="s">
+        <v>445</v>
+      </c>
+      <c r="H74" t="s">
+        <v>446</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" t="s">
         <v>447</v>
       </c>
-      <c r="H74" t="s">
+      <c r="K74" t="s">
         <v>448</v>
       </c>
-      <c r="I74" t="b">
-        <v>0</v>
-      </c>
-      <c r="J74" t="s">
+      <c r="L74" t="s">
         <v>449</v>
-      </c>
-      <c r="K74" t="s">
-        <v>450</v>
-      </c>
-      <c r="L74" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
@@ -6836,13 +6830,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E75">
         <v>123456789012</v>
@@ -6851,22 +6845,22 @@
         <v>3214569870</v>
       </c>
       <c r="G75" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H75" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I75" t="b">
         <v>1</v>
       </c>
       <c r="J75" t="s">
+        <v>453</v>
+      </c>
+      <c r="K75" t="s">
+        <v>454</v>
+      </c>
+      <c r="L75" t="s">
         <v>455</v>
-      </c>
-      <c r="K75" t="s">
-        <v>456</v>
-      </c>
-      <c r="L75" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
@@ -6874,7 +6868,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C76">
         <v>7</v>
@@ -6889,22 +6883,22 @@
         <v>7890456123</v>
       </c>
       <c r="G76" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H76" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I76" t="b">
         <v>1</v>
       </c>
       <c r="J76" t="s">
+        <v>459</v>
+      </c>
+      <c r="K76" t="s">
+        <v>460</v>
+      </c>
+      <c r="L76" t="s">
         <v>461</v>
-      </c>
-      <c r="K76" t="s">
-        <v>462</v>
-      </c>
-      <c r="L76" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
@@ -6912,13 +6906,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C77">
         <v>8</v>
       </c>
       <c r="D77" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E77">
         <v>345678901234</v>
@@ -6927,22 +6921,22 @@
         <v>3214569870</v>
       </c>
       <c r="G77" t="s">
+        <v>463</v>
+      </c>
+      <c r="H77" t="s">
+        <v>464</v>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" t="s">
         <v>465</v>
       </c>
-      <c r="H77" t="s">
+      <c r="K77" t="s">
         <v>466</v>
       </c>
-      <c r="I77" t="b">
-        <v>0</v>
-      </c>
-      <c r="J77" t="s">
+      <c r="L77" t="s">
         <v>467</v>
-      </c>
-      <c r="K77" t="s">
-        <v>468</v>
-      </c>
-      <c r="L77" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
@@ -6950,13 +6944,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E78">
         <v>123456789012</v>
@@ -6965,22 +6959,22 @@
         <v>7412589630</v>
       </c>
       <c r="G78" t="s">
+        <v>469</v>
+      </c>
+      <c r="H78" t="s">
+        <v>470</v>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78" t="s">
         <v>471</v>
       </c>
-      <c r="H78" t="s">
+      <c r="K78" t="s">
         <v>472</v>
       </c>
-      <c r="I78" t="b">
-        <v>0</v>
-      </c>
-      <c r="J78" t="s">
+      <c r="L78" t="s">
         <v>473</v>
-      </c>
-      <c r="K78" t="s">
-        <v>474</v>
-      </c>
-      <c r="L78" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
@@ -6988,7 +6982,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -7003,22 +6997,22 @@
         <v>7890456123</v>
       </c>
       <c r="G79" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="H79" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="I79" t="b">
         <v>1</v>
       </c>
       <c r="J79" t="s">
+        <v>477</v>
+      </c>
+      <c r="K79" t="s">
+        <v>478</v>
+      </c>
+      <c r="L79" t="s">
         <v>479</v>
-      </c>
-      <c r="K79" t="s">
-        <v>480</v>
-      </c>
-      <c r="L79" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
@@ -7026,13 +7020,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C80">
         <v>9</v>
       </c>
       <c r="D80" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E80">
         <v>567890123456</v>
@@ -7041,22 +7035,22 @@
         <v>3214569870</v>
       </c>
       <c r="G80" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="H80" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="I80" t="b">
         <v>1</v>
       </c>
       <c r="J80" t="s">
+        <v>483</v>
+      </c>
+      <c r="K80" t="s">
+        <v>484</v>
+      </c>
+      <c r="L80" t="s">
         <v>485</v>
-      </c>
-      <c r="K80" t="s">
-        <v>486</v>
-      </c>
-      <c r="L80" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
@@ -7064,7 +7058,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C81">
         <v>2</v>
@@ -7079,22 +7073,22 @@
         <v>7890456123</v>
       </c>
       <c r="G81" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H81" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I81" t="b">
         <v>1</v>
       </c>
       <c r="J81" t="s">
+        <v>489</v>
+      </c>
+      <c r="K81" t="s">
+        <v>490</v>
+      </c>
+      <c r="L81" t="s">
         <v>491</v>
-      </c>
-      <c r="K81" t="s">
-        <v>492</v>
-      </c>
-      <c r="L81" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
@@ -7102,13 +7096,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C82">
         <v>9</v>
       </c>
       <c r="D82" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E82">
         <v>567890123456</v>
@@ -7117,22 +7111,22 @@
         <v>3214569870</v>
       </c>
       <c r="G82" t="s">
+        <v>493</v>
+      </c>
+      <c r="H82" t="s">
+        <v>494</v>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+      <c r="J82" t="s">
         <v>495</v>
       </c>
-      <c r="H82" t="s">
+      <c r="K82" t="s">
         <v>496</v>
       </c>
-      <c r="I82" t="b">
-        <v>0</v>
-      </c>
-      <c r="J82" t="s">
+      <c r="L82" t="s">
         <v>497</v>
-      </c>
-      <c r="K82" t="s">
-        <v>498</v>
-      </c>
-      <c r="L82" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
@@ -7140,13 +7134,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C83">
         <v>7</v>
       </c>
       <c r="D83" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E83">
         <v>345678901234</v>
@@ -7155,22 +7149,22 @@
         <v>7890456123</v>
       </c>
       <c r="G83" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H83" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I83" t="b">
         <v>1</v>
       </c>
       <c r="J83" t="s">
+        <v>501</v>
+      </c>
+      <c r="K83" t="s">
+        <v>502</v>
+      </c>
+      <c r="L83" t="s">
         <v>503</v>
-      </c>
-      <c r="K83" t="s">
-        <v>504</v>
-      </c>
-      <c r="L83" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
@@ -7178,7 +7172,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C84">
         <v>6</v>
@@ -7193,22 +7187,22 @@
         <v>7890456123</v>
       </c>
       <c r="G84" t="s">
+        <v>505</v>
+      </c>
+      <c r="H84" t="s">
+        <v>506</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84" t="s">
         <v>507</v>
       </c>
-      <c r="H84" t="s">
+      <c r="K84" t="s">
         <v>508</v>
       </c>
-      <c r="I84" t="b">
-        <v>0</v>
-      </c>
-      <c r="J84" t="s">
+      <c r="L84" t="s">
         <v>509</v>
-      </c>
-      <c r="K84" t="s">
-        <v>510</v>
-      </c>
-      <c r="L84" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
@@ -7216,13 +7210,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C85">
         <v>5</v>
       </c>
       <c r="D85" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E85">
         <v>567890123456</v>
@@ -7231,22 +7225,22 @@
         <v>3214569870</v>
       </c>
       <c r="G85" t="s">
+        <v>511</v>
+      </c>
+      <c r="H85" t="s">
+        <v>512</v>
+      </c>
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+      <c r="J85" t="s">
         <v>513</v>
       </c>
-      <c r="H85" t="s">
+      <c r="K85" t="s">
         <v>514</v>
       </c>
-      <c r="I85" t="b">
-        <v>0</v>
-      </c>
-      <c r="J85" t="s">
+      <c r="L85" t="s">
         <v>515</v>
-      </c>
-      <c r="K85" t="s">
-        <v>516</v>
-      </c>
-      <c r="L85" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
@@ -7254,13 +7248,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E86">
         <v>123456789012</v>
@@ -7269,22 +7263,22 @@
         <v>7890456123</v>
       </c>
       <c r="G86" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H86" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="I86" t="b">
         <v>1</v>
       </c>
       <c r="J86" t="s">
+        <v>519</v>
+      </c>
+      <c r="K86" t="s">
+        <v>520</v>
+      </c>
+      <c r="L86" t="s">
         <v>521</v>
-      </c>
-      <c r="K86" t="s">
-        <v>522</v>
-      </c>
-      <c r="L86" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
@@ -7292,13 +7286,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C87">
         <v>4</v>
       </c>
       <c r="D87" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E87">
         <v>345678901234</v>
@@ -7307,22 +7301,22 @@
         <v>7412589630</v>
       </c>
       <c r="G87" t="s">
+        <v>523</v>
+      </c>
+      <c r="H87" t="s">
+        <v>524</v>
+      </c>
+      <c r="I87" t="b">
+        <v>0</v>
+      </c>
+      <c r="J87" t="s">
         <v>525</v>
       </c>
-      <c r="H87" t="s">
+      <c r="K87" t="s">
         <v>526</v>
       </c>
-      <c r="I87" t="b">
-        <v>0</v>
-      </c>
-      <c r="J87" t="s">
+      <c r="L87" t="s">
         <v>527</v>
-      </c>
-      <c r="K87" t="s">
-        <v>528</v>
-      </c>
-      <c r="L87" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
@@ -7330,13 +7324,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E88">
         <v>567890123456</v>
@@ -7345,22 +7339,22 @@
         <v>3214569870</v>
       </c>
       <c r="G88" t="s">
+        <v>529</v>
+      </c>
+      <c r="H88" t="s">
+        <v>530</v>
+      </c>
+      <c r="I88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" t="s">
         <v>531</v>
       </c>
-      <c r="H88" t="s">
+      <c r="K88" t="s">
         <v>532</v>
       </c>
-      <c r="I88" t="b">
-        <v>0</v>
-      </c>
-      <c r="J88" t="s">
+      <c r="L88" t="s">
         <v>533</v>
-      </c>
-      <c r="K88" t="s">
-        <v>534</v>
-      </c>
-      <c r="L88" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
@@ -7368,13 +7362,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C89">
         <v>2</v>
       </c>
       <c r="D89" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E89">
         <v>567890123456</v>
@@ -7383,22 +7377,22 @@
         <v>7412589630</v>
       </c>
       <c r="G89" t="s">
+        <v>535</v>
+      </c>
+      <c r="H89" t="s">
+        <v>536</v>
+      </c>
+      <c r="I89" t="b">
+        <v>0</v>
+      </c>
+      <c r="J89" t="s">
         <v>537</v>
       </c>
-      <c r="H89" t="s">
+      <c r="K89" t="s">
         <v>538</v>
       </c>
-      <c r="I89" t="b">
-        <v>0</v>
-      </c>
-      <c r="J89" t="s">
+      <c r="L89" t="s">
         <v>539</v>
-      </c>
-      <c r="K89" t="s">
-        <v>540</v>
-      </c>
-      <c r="L89" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
@@ -7406,13 +7400,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C90">
         <v>8</v>
       </c>
       <c r="D90" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E90">
         <v>345678901234</v>
@@ -7421,22 +7415,22 @@
         <v>7890456123</v>
       </c>
       <c r="G90" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H90" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="I90" t="b">
         <v>1</v>
       </c>
       <c r="J90" t="s">
+        <v>543</v>
+      </c>
+      <c r="K90" t="s">
+        <v>544</v>
+      </c>
+      <c r="L90" t="s">
         <v>545</v>
-      </c>
-      <c r="K90" t="s">
-        <v>546</v>
-      </c>
-      <c r="L90" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
@@ -7444,7 +7438,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -7459,22 +7453,22 @@
         <v>7890456123</v>
       </c>
       <c r="G91" t="s">
+        <v>547</v>
+      </c>
+      <c r="H91" t="s">
+        <v>548</v>
+      </c>
+      <c r="I91" t="b">
+        <v>0</v>
+      </c>
+      <c r="J91" t="s">
         <v>549</v>
       </c>
-      <c r="H91" t="s">
+      <c r="K91" t="s">
         <v>550</v>
       </c>
-      <c r="I91" t="b">
-        <v>0</v>
-      </c>
-      <c r="J91" t="s">
+      <c r="L91" t="s">
         <v>551</v>
-      </c>
-      <c r="K91" t="s">
-        <v>552</v>
-      </c>
-      <c r="L91" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
@@ -7482,13 +7476,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C92">
         <v>9</v>
       </c>
       <c r="D92" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E92">
         <v>345678901234</v>
@@ -7497,22 +7491,22 @@
         <v>3214569870</v>
       </c>
       <c r="G92" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="H92" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="I92" t="b">
         <v>1</v>
       </c>
       <c r="J92" t="s">
+        <v>555</v>
+      </c>
+      <c r="K92" t="s">
+        <v>556</v>
+      </c>
+      <c r="L92" t="s">
         <v>557</v>
-      </c>
-      <c r="K92" t="s">
-        <v>558</v>
-      </c>
-      <c r="L92" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
@@ -7520,13 +7514,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C93">
         <v>5</v>
       </c>
       <c r="D93" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E93">
         <v>345678901234</v>
@@ -7535,22 +7529,22 @@
         <v>3214569870</v>
       </c>
       <c r="G93" t="s">
+        <v>559</v>
+      </c>
+      <c r="H93" t="s">
+        <v>560</v>
+      </c>
+      <c r="I93" t="b">
+        <v>0</v>
+      </c>
+      <c r="J93" t="s">
         <v>561</v>
       </c>
-      <c r="H93" t="s">
+      <c r="K93" t="s">
         <v>562</v>
       </c>
-      <c r="I93" t="b">
-        <v>0</v>
-      </c>
-      <c r="J93" t="s">
+      <c r="L93" t="s">
         <v>563</v>
-      </c>
-      <c r="K93" t="s">
-        <v>564</v>
-      </c>
-      <c r="L93" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
@@ -7558,13 +7552,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C94">
         <v>3</v>
       </c>
       <c r="D94" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E94">
         <v>123456789012</v>
@@ -7573,22 +7567,22 @@
         <v>3214569870</v>
       </c>
       <c r="G94" t="s">
+        <v>565</v>
+      </c>
+      <c r="H94" t="s">
+        <v>566</v>
+      </c>
+      <c r="I94" t="b">
+        <v>0</v>
+      </c>
+      <c r="J94" t="s">
         <v>567</v>
       </c>
-      <c r="H94" t="s">
+      <c r="K94" t="s">
         <v>568</v>
       </c>
-      <c r="I94" t="b">
-        <v>0</v>
-      </c>
-      <c r="J94" t="s">
+      <c r="L94" t="s">
         <v>569</v>
-      </c>
-      <c r="K94" t="s">
-        <v>570</v>
-      </c>
-      <c r="L94" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
@@ -7596,7 +7590,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C95">
         <v>2</v>
@@ -7611,22 +7605,22 @@
         <v>7412589630</v>
       </c>
       <c r="G95" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H95" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="I95" t="b">
         <v>1</v>
       </c>
       <c r="J95" t="s">
+        <v>573</v>
+      </c>
+      <c r="K95" t="s">
+        <v>574</v>
+      </c>
+      <c r="L95" t="s">
         <v>575</v>
-      </c>
-      <c r="K95" t="s">
-        <v>576</v>
-      </c>
-      <c r="L95" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
@@ -7634,7 +7628,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C96">
         <v>3</v>
@@ -7649,22 +7643,22 @@
         <v>3214569870</v>
       </c>
       <c r="G96" t="s">
+        <v>577</v>
+      </c>
+      <c r="H96" t="s">
+        <v>578</v>
+      </c>
+      <c r="I96" t="b">
+        <v>0</v>
+      </c>
+      <c r="J96" t="s">
         <v>579</v>
       </c>
-      <c r="H96" t="s">
+      <c r="K96" t="s">
         <v>580</v>
       </c>
-      <c r="I96" t="b">
-        <v>0</v>
-      </c>
-      <c r="J96" t="s">
+      <c r="L96" t="s">
         <v>581</v>
-      </c>
-      <c r="K96" t="s">
-        <v>582</v>
-      </c>
-      <c r="L96" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
@@ -7672,13 +7666,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C97">
         <v>1</v>
       </c>
       <c r="D97" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E97">
         <v>123456789012</v>
@@ -7687,22 +7681,22 @@
         <v>7412589630</v>
       </c>
       <c r="G97" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H97" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="I97" t="b">
         <v>1</v>
       </c>
       <c r="J97" t="s">
+        <v>585</v>
+      </c>
+      <c r="K97" t="s">
+        <v>586</v>
+      </c>
+      <c r="L97" t="s">
         <v>587</v>
-      </c>
-      <c r="K97" t="s">
-        <v>588</v>
-      </c>
-      <c r="L97" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
@@ -7710,13 +7704,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C98">
         <v>1</v>
       </c>
       <c r="D98" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E98">
         <v>123456789012</v>
@@ -7725,22 +7719,22 @@
         <v>7412589630</v>
       </c>
       <c r="G98" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="H98" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="I98" t="b">
         <v>1</v>
       </c>
       <c r="J98" t="s">
+        <v>591</v>
+      </c>
+      <c r="K98" t="s">
+        <v>592</v>
+      </c>
+      <c r="L98" t="s">
         <v>593</v>
-      </c>
-      <c r="K98" t="s">
-        <v>594</v>
-      </c>
-      <c r="L98" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
@@ -7748,13 +7742,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C99">
         <v>4</v>
       </c>
       <c r="D99" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E99">
         <v>345678901234</v>
@@ -7763,22 +7757,22 @@
         <v>3214569870</v>
       </c>
       <c r="G99" t="s">
+        <v>595</v>
+      </c>
+      <c r="H99" t="s">
+        <v>596</v>
+      </c>
+      <c r="I99" t="b">
+        <v>0</v>
+      </c>
+      <c r="J99" t="s">
         <v>597</v>
       </c>
-      <c r="H99" t="s">
+      <c r="K99" t="s">
         <v>598</v>
       </c>
-      <c r="I99" t="b">
-        <v>0</v>
-      </c>
-      <c r="J99" t="s">
+      <c r="L99" t="s">
         <v>599</v>
-      </c>
-      <c r="K99" t="s">
-        <v>600</v>
-      </c>
-      <c r="L99" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
@@ -7786,7 +7780,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C100">
         <v>9</v>
@@ -7801,22 +7795,22 @@
         <v>3214569870</v>
       </c>
       <c r="G100" t="s">
+        <v>601</v>
+      </c>
+      <c r="H100" t="s">
+        <v>602</v>
+      </c>
+      <c r="I100" t="b">
+        <v>0</v>
+      </c>
+      <c r="J100" t="s">
         <v>603</v>
       </c>
-      <c r="H100" t="s">
+      <c r="K100" t="s">
         <v>604</v>
       </c>
-      <c r="I100" t="b">
-        <v>0</v>
-      </c>
-      <c r="J100" t="s">
+      <c r="L100" t="s">
         <v>605</v>
-      </c>
-      <c r="K100" t="s">
-        <v>606</v>
-      </c>
-      <c r="L100" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
@@ -7824,13 +7818,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C101">
         <v>7</v>
       </c>
       <c r="D101" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E101">
         <v>345678901234</v>
@@ -7839,22 +7833,22 @@
         <v>3214569870</v>
       </c>
       <c r="G101" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="H101" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="I101" t="b">
         <v>1</v>
       </c>
       <c r="J101" t="s">
+        <v>609</v>
+      </c>
+      <c r="K101" t="s">
+        <v>610</v>
+      </c>
+      <c r="L101" t="s">
         <v>611</v>
-      </c>
-      <c r="K101" t="s">
-        <v>612</v>
-      </c>
-      <c r="L101" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
@@ -7862,13 +7856,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C102">
         <v>3</v>
       </c>
       <c r="D102" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E102">
         <v>567890123456</v>
@@ -7877,22 +7871,22 @@
         <v>3214569870</v>
       </c>
       <c r="G102" t="s">
+        <v>613</v>
+      </c>
+      <c r="H102" t="s">
+        <v>614</v>
+      </c>
+      <c r="I102" t="b">
+        <v>0</v>
+      </c>
+      <c r="J102" t="s">
         <v>615</v>
       </c>
-      <c r="H102" t="s">
+      <c r="K102" t="s">
         <v>616</v>
       </c>
-      <c r="I102" t="b">
-        <v>0</v>
-      </c>
-      <c r="J102" t="s">
+      <c r="L102" t="s">
         <v>617</v>
-      </c>
-      <c r="K102" t="s">
-        <v>618</v>
-      </c>
-      <c r="L102" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
@@ -7900,13 +7894,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C103">
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E103">
         <v>567890123456</v>
@@ -7915,22 +7909,22 @@
         <v>7412589630</v>
       </c>
       <c r="G103" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H103" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="I103" t="b">
         <v>1</v>
       </c>
       <c r="J103" t="s">
+        <v>621</v>
+      </c>
+      <c r="K103" t="s">
+        <v>622</v>
+      </c>
+      <c r="L103" t="s">
         <v>623</v>
-      </c>
-      <c r="K103" t="s">
-        <v>624</v>
-      </c>
-      <c r="L103" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
@@ -7938,7 +7932,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C104">
         <v>3</v>
@@ -7953,22 +7947,22 @@
         <v>7890456123</v>
       </c>
       <c r="G104" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="H104" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="I104" t="b">
         <v>1</v>
       </c>
       <c r="J104" t="s">
+        <v>627</v>
+      </c>
+      <c r="K104" t="s">
+        <v>628</v>
+      </c>
+      <c r="L104" t="s">
         <v>629</v>
-      </c>
-      <c r="K104" t="s">
-        <v>630</v>
-      </c>
-      <c r="L104" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
@@ -7976,13 +7970,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C105">
         <v>4</v>
       </c>
       <c r="D105" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E105">
         <v>345678901234</v>
@@ -7991,22 +7985,22 @@
         <v>7412589630</v>
       </c>
       <c r="G105" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="H105" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="I105" t="b">
         <v>1</v>
       </c>
       <c r="J105" t="s">
+        <v>633</v>
+      </c>
+      <c r="K105" t="s">
+        <v>634</v>
+      </c>
+      <c r="L105" t="s">
         <v>635</v>
-      </c>
-      <c r="K105" t="s">
-        <v>636</v>
-      </c>
-      <c r="L105" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
@@ -8014,7 +8008,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C106">
         <v>6</v>
@@ -8029,22 +8023,22 @@
         <v>7890456123</v>
       </c>
       <c r="G106" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H106" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="I106" t="b">
         <v>1</v>
       </c>
       <c r="J106" t="s">
+        <v>639</v>
+      </c>
+      <c r="K106" t="s">
+        <v>640</v>
+      </c>
+      <c r="L106" t="s">
         <v>641</v>
-      </c>
-      <c r="K106" t="s">
-        <v>642</v>
-      </c>
-      <c r="L106" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
@@ -8052,13 +8046,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C107">
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E107">
         <v>345678901234</v>
@@ -8067,22 +8061,22 @@
         <v>7890456123</v>
       </c>
       <c r="G107" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="H107" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="I107" t="b">
         <v>1</v>
       </c>
       <c r="J107" t="s">
+        <v>645</v>
+      </c>
+      <c r="K107" t="s">
+        <v>646</v>
+      </c>
+      <c r="L107" t="s">
         <v>647</v>
-      </c>
-      <c r="K107" t="s">
-        <v>648</v>
-      </c>
-      <c r="L107" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
@@ -8090,7 +8084,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C108">
         <v>9</v>
@@ -8105,22 +8099,22 @@
         <v>7890456123</v>
       </c>
       <c r="G108" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H108" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="I108" t="b">
         <v>1</v>
       </c>
       <c r="J108" t="s">
+        <v>651</v>
+      </c>
+      <c r="K108" t="s">
+        <v>652</v>
+      </c>
+      <c r="L108" t="s">
         <v>653</v>
-      </c>
-      <c r="K108" t="s">
-        <v>654</v>
-      </c>
-      <c r="L108" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
@@ -8128,13 +8122,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C109">
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E109">
         <v>345678901234</v>
@@ -8143,22 +8137,22 @@
         <v>7412589630</v>
       </c>
       <c r="G109" t="s">
+        <v>655</v>
+      </c>
+      <c r="H109" t="s">
+        <v>656</v>
+      </c>
+      <c r="I109" t="b">
+        <v>0</v>
+      </c>
+      <c r="J109" t="s">
         <v>657</v>
       </c>
-      <c r="H109" t="s">
+      <c r="K109" t="s">
         <v>658</v>
       </c>
-      <c r="I109" t="b">
-        <v>0</v>
-      </c>
-      <c r="J109" t="s">
+      <c r="L109" t="s">
         <v>659</v>
-      </c>
-      <c r="K109" t="s">
-        <v>660</v>
-      </c>
-      <c r="L109" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
@@ -8166,7 +8160,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C110">
         <v>7</v>
@@ -8181,22 +8175,22 @@
         <v>3214569870</v>
       </c>
       <c r="G110" t="s">
+        <v>661</v>
+      </c>
+      <c r="H110" t="s">
+        <v>662</v>
+      </c>
+      <c r="I110" t="b">
+        <v>0</v>
+      </c>
+      <c r="J110" t="s">
         <v>663</v>
       </c>
-      <c r="H110" t="s">
+      <c r="K110" t="s">
         <v>664</v>
       </c>
-      <c r="I110" t="b">
-        <v>0</v>
-      </c>
-      <c r="J110" t="s">
+      <c r="L110" t="s">
         <v>665</v>
-      </c>
-      <c r="K110" t="s">
-        <v>666</v>
-      </c>
-      <c r="L110" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
@@ -8204,13 +8198,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C111">
         <v>5</v>
       </c>
       <c r="D111" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E111">
         <v>345678901234</v>
@@ -8219,22 +8213,22 @@
         <v>7412589630</v>
       </c>
       <c r="G111" t="s">
+        <v>667</v>
+      </c>
+      <c r="H111" t="s">
+        <v>668</v>
+      </c>
+      <c r="I111" t="b">
+        <v>0</v>
+      </c>
+      <c r="J111" t="s">
         <v>669</v>
       </c>
-      <c r="H111" t="s">
+      <c r="K111" t="s">
         <v>670</v>
       </c>
-      <c r="I111" t="b">
-        <v>0</v>
-      </c>
-      <c r="J111" t="s">
+      <c r="L111" t="s">
         <v>671</v>
-      </c>
-      <c r="K111" t="s">
-        <v>672</v>
-      </c>
-      <c r="L111" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
@@ -8242,13 +8236,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C112">
         <v>6</v>
       </c>
       <c r="D112" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E112">
         <v>345678901234</v>
@@ -8257,22 +8251,22 @@
         <v>3214569870</v>
       </c>
       <c r="G112" t="s">
+        <v>673</v>
+      </c>
+      <c r="H112" t="s">
+        <v>674</v>
+      </c>
+      <c r="I112" t="b">
+        <v>0</v>
+      </c>
+      <c r="J112" t="s">
         <v>675</v>
       </c>
-      <c r="H112" t="s">
+      <c r="K112" t="s">
         <v>676</v>
       </c>
-      <c r="I112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J112" t="s">
+      <c r="L112" t="s">
         <v>677</v>
-      </c>
-      <c r="K112" t="s">
-        <v>678</v>
-      </c>
-      <c r="L112" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.2">
@@ -8280,13 +8274,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C113">
         <v>3</v>
       </c>
       <c r="D113" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E113">
         <v>345678901234</v>
@@ -8295,22 +8289,22 @@
         <v>7412589630</v>
       </c>
       <c r="G113" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H113" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="I113" t="b">
         <v>1</v>
       </c>
       <c r="J113" t="s">
+        <v>681</v>
+      </c>
+      <c r="K113" t="s">
+        <v>682</v>
+      </c>
+      <c r="L113" t="s">
         <v>683</v>
-      </c>
-      <c r="K113" t="s">
-        <v>684</v>
-      </c>
-      <c r="L113" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.2">
@@ -8318,13 +8312,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C114">
         <v>4</v>
       </c>
       <c r="D114" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E114">
         <v>345678901234</v>
@@ -8333,22 +8327,22 @@
         <v>3214569870</v>
       </c>
       <c r="G114" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="H114" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="I114" t="b">
         <v>1</v>
       </c>
       <c r="J114" t="s">
+        <v>687</v>
+      </c>
+      <c r="K114" t="s">
+        <v>688</v>
+      </c>
+      <c r="L114" t="s">
         <v>689</v>
-      </c>
-      <c r="K114" t="s">
-        <v>690</v>
-      </c>
-      <c r="L114" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.2">
@@ -8356,13 +8350,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C115">
         <v>4</v>
       </c>
       <c r="D115" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E115">
         <v>567890123456</v>
@@ -8371,22 +8365,22 @@
         <v>7890456123</v>
       </c>
       <c r="G115" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H115" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="I115" t="b">
         <v>1</v>
       </c>
       <c r="J115" t="s">
+        <v>693</v>
+      </c>
+      <c r="K115" t="s">
+        <v>694</v>
+      </c>
+      <c r="L115" t="s">
         <v>695</v>
-      </c>
-      <c r="K115" t="s">
-        <v>696</v>
-      </c>
-      <c r="L115" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.2">
@@ -8394,13 +8388,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C116">
         <v>3</v>
       </c>
       <c r="D116" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E116">
         <v>345678901234</v>
@@ -8409,22 +8403,22 @@
         <v>3214569870</v>
       </c>
       <c r="G116" t="s">
+        <v>697</v>
+      </c>
+      <c r="H116" t="s">
+        <v>698</v>
+      </c>
+      <c r="I116" t="b">
+        <v>0</v>
+      </c>
+      <c r="J116" t="s">
         <v>699</v>
       </c>
-      <c r="H116" t="s">
+      <c r="K116" t="s">
         <v>700</v>
       </c>
-      <c r="I116" t="b">
-        <v>0</v>
-      </c>
-      <c r="J116" t="s">
+      <c r="L116" t="s">
         <v>701</v>
-      </c>
-      <c r="K116" t="s">
-        <v>702</v>
-      </c>
-      <c r="L116" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.2">
@@ -8432,13 +8426,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C117">
         <v>7</v>
       </c>
       <c r="D117" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E117">
         <v>567890123456</v>
@@ -8447,22 +8441,22 @@
         <v>7412589630</v>
       </c>
       <c r="G117" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H117" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="I117" t="b">
         <v>1</v>
       </c>
       <c r="J117" t="s">
+        <v>705</v>
+      </c>
+      <c r="K117" t="s">
+        <v>706</v>
+      </c>
+      <c r="L117" t="s">
         <v>707</v>
-      </c>
-      <c r="K117" t="s">
-        <v>708</v>
-      </c>
-      <c r="L117" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.2">
@@ -8470,13 +8464,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C118">
         <v>8</v>
       </c>
       <c r="D118" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E118">
         <v>567890123456</v>
@@ -8485,22 +8479,22 @@
         <v>7890456123</v>
       </c>
       <c r="G118" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H118" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="I118" t="b">
         <v>1</v>
       </c>
       <c r="J118" t="s">
+        <v>710</v>
+      </c>
+      <c r="K118" t="s">
+        <v>711</v>
+      </c>
+      <c r="L118" t="s">
         <v>712</v>
-      </c>
-      <c r="K118" t="s">
-        <v>713</v>
-      </c>
-      <c r="L118" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.2">
@@ -8508,13 +8502,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C119">
         <v>2</v>
       </c>
       <c r="D119" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E119">
         <v>567890123456</v>
@@ -8523,22 +8517,22 @@
         <v>3214569870</v>
       </c>
       <c r="G119" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H119" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="I119" t="b">
         <v>1</v>
       </c>
       <c r="J119" t="s">
+        <v>716</v>
+      </c>
+      <c r="K119" t="s">
+        <v>717</v>
+      </c>
+      <c r="L119" t="s">
         <v>718</v>
-      </c>
-      <c r="K119" t="s">
-        <v>719</v>
-      </c>
-      <c r="L119" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.2">
@@ -8546,7 +8540,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C120">
         <v>5</v>
@@ -8561,22 +8555,22 @@
         <v>7412589630</v>
       </c>
       <c r="G120" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="H120" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="I120" t="b">
         <v>1</v>
       </c>
       <c r="J120" t="s">
+        <v>722</v>
+      </c>
+      <c r="K120" t="s">
+        <v>723</v>
+      </c>
+      <c r="L120" t="s">
         <v>724</v>
-      </c>
-      <c r="K120" t="s">
-        <v>725</v>
-      </c>
-      <c r="L120" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.2">
@@ -8584,13 +8578,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C121">
         <v>7</v>
       </c>
       <c r="D121" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E121">
         <v>567890123456</v>
@@ -8599,22 +8593,22 @@
         <v>7412589630</v>
       </c>
       <c r="G121" t="s">
+        <v>726</v>
+      </c>
+      <c r="H121" t="s">
+        <v>727</v>
+      </c>
+      <c r="I121" t="b">
+        <v>0</v>
+      </c>
+      <c r="J121" t="s">
         <v>728</v>
       </c>
-      <c r="H121" t="s">
+      <c r="K121" t="s">
         <v>729</v>
       </c>
-      <c r="I121" t="b">
-        <v>0</v>
-      </c>
-      <c r="J121" t="s">
+      <c r="L121" t="s">
         <v>730</v>
-      </c>
-      <c r="K121" t="s">
-        <v>731</v>
-      </c>
-      <c r="L121" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.2">
@@ -8622,13 +8616,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C122">
         <v>0</v>
       </c>
       <c r="D122" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E122">
         <v>123456789012</v>
@@ -8637,22 +8631,22 @@
         <v>3214569870</v>
       </c>
       <c r="G122" t="s">
+        <v>732</v>
+      </c>
+      <c r="H122" t="s">
+        <v>733</v>
+      </c>
+      <c r="I122" t="b">
+        <v>0</v>
+      </c>
+      <c r="J122" t="s">
         <v>734</v>
       </c>
-      <c r="H122" t="s">
+      <c r="K122" t="s">
         <v>735</v>
       </c>
-      <c r="I122" t="b">
-        <v>0</v>
-      </c>
-      <c r="J122" t="s">
+      <c r="L122" t="s">
         <v>736</v>
-      </c>
-      <c r="K122" t="s">
-        <v>737</v>
-      </c>
-      <c r="L122" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.2">
@@ -8660,13 +8654,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C123">
         <v>6</v>
       </c>
       <c r="D123" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E123">
         <v>567890123456</v>
@@ -8675,22 +8669,22 @@
         <v>7412589630</v>
       </c>
       <c r="G123" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="H123" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="I123" t="b">
         <v>1</v>
       </c>
       <c r="J123" t="s">
+        <v>740</v>
+      </c>
+      <c r="K123" t="s">
+        <v>741</v>
+      </c>
+      <c r="L123" t="s">
         <v>742</v>
-      </c>
-      <c r="K123" t="s">
-        <v>743</v>
-      </c>
-      <c r="L123" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.2">
@@ -8698,13 +8692,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C124">
         <v>4</v>
       </c>
       <c r="D124" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E124">
         <v>123456789012</v>
@@ -8713,22 +8707,22 @@
         <v>3214569870</v>
       </c>
       <c r="G124" t="s">
+        <v>744</v>
+      </c>
+      <c r="H124" t="s">
+        <v>745</v>
+      </c>
+      <c r="I124" t="b">
+        <v>0</v>
+      </c>
+      <c r="J124" t="s">
         <v>746</v>
       </c>
-      <c r="H124" t="s">
+      <c r="K124" t="s">
         <v>747</v>
       </c>
-      <c r="I124" t="b">
-        <v>0</v>
-      </c>
-      <c r="J124" t="s">
+      <c r="L124" t="s">
         <v>748</v>
-      </c>
-      <c r="K124" t="s">
-        <v>749</v>
-      </c>
-      <c r="L124" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.2">
@@ -8736,13 +8730,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C125">
         <v>1</v>
       </c>
       <c r="D125" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E125">
         <v>345678901234</v>
@@ -8751,22 +8745,22 @@
         <v>3214569870</v>
       </c>
       <c r="G125" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="H125" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="I125" t="b">
         <v>1</v>
       </c>
       <c r="J125" t="s">
+        <v>751</v>
+      </c>
+      <c r="K125" t="s">
+        <v>752</v>
+      </c>
+      <c r="L125" t="s">
         <v>753</v>
-      </c>
-      <c r="K125" t="s">
-        <v>754</v>
-      </c>
-      <c r="L125" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
@@ -8774,13 +8768,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C126">
         <v>0</v>
       </c>
       <c r="D126" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E126">
         <v>567890123456</v>
@@ -8789,22 +8783,22 @@
         <v>7412589630</v>
       </c>
       <c r="G126" t="s">
+        <v>755</v>
+      </c>
+      <c r="H126" t="s">
+        <v>756</v>
+      </c>
+      <c r="I126" t="b">
+        <v>0</v>
+      </c>
+      <c r="J126" t="s">
         <v>757</v>
       </c>
-      <c r="H126" t="s">
+      <c r="K126" t="s">
         <v>758</v>
       </c>
-      <c r="I126" t="b">
-        <v>0</v>
-      </c>
-      <c r="J126" t="s">
+      <c r="L126" t="s">
         <v>759</v>
-      </c>
-      <c r="K126" t="s">
-        <v>760</v>
-      </c>
-      <c r="L126" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
@@ -8812,7 +8806,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C127">
         <v>8</v>
@@ -8827,22 +8821,22 @@
         <v>3214569870</v>
       </c>
       <c r="G127" t="s">
+        <v>761</v>
+      </c>
+      <c r="H127" t="s">
+        <v>762</v>
+      </c>
+      <c r="I127" t="b">
+        <v>0</v>
+      </c>
+      <c r="J127" t="s">
         <v>763</v>
       </c>
-      <c r="H127" t="s">
+      <c r="K127" t="s">
         <v>764</v>
       </c>
-      <c r="I127" t="b">
-        <v>0</v>
-      </c>
-      <c r="J127" t="s">
+      <c r="L127" t="s">
         <v>765</v>
-      </c>
-      <c r="K127" t="s">
-        <v>766</v>
-      </c>
-      <c r="L127" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
@@ -8850,7 +8844,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C128">
         <v>3</v>
@@ -8865,22 +8859,22 @@
         <v>3214569870</v>
       </c>
       <c r="G128" t="s">
+        <v>767</v>
+      </c>
+      <c r="H128" t="s">
+        <v>768</v>
+      </c>
+      <c r="I128" t="b">
+        <v>0</v>
+      </c>
+      <c r="J128" t="s">
         <v>769</v>
       </c>
-      <c r="H128" t="s">
+      <c r="K128" t="s">
         <v>770</v>
       </c>
-      <c r="I128" t="b">
-        <v>0</v>
-      </c>
-      <c r="J128" t="s">
+      <c r="L128" t="s">
         <v>771</v>
-      </c>
-      <c r="K128" t="s">
-        <v>772</v>
-      </c>
-      <c r="L128" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
@@ -8888,7 +8882,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -8903,22 +8897,22 @@
         <v>7412589630</v>
       </c>
       <c r="G129" t="s">
+        <v>773</v>
+      </c>
+      <c r="H129" t="s">
+        <v>774</v>
+      </c>
+      <c r="I129" t="b">
+        <v>0</v>
+      </c>
+      <c r="J129" t="s">
         <v>775</v>
       </c>
-      <c r="H129" t="s">
+      <c r="K129" t="s">
         <v>776</v>
       </c>
-      <c r="I129" t="b">
-        <v>0</v>
-      </c>
-      <c r="J129" t="s">
+      <c r="L129" t="s">
         <v>777</v>
-      </c>
-      <c r="K129" t="s">
-        <v>778</v>
-      </c>
-      <c r="L129" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
@@ -8926,13 +8920,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C130">
         <v>0</v>
       </c>
       <c r="D130" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E130">
         <v>345678901234</v>
@@ -8941,22 +8935,22 @@
         <v>7890456123</v>
       </c>
       <c r="G130" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="H130" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="I130" t="b">
         <v>1</v>
       </c>
       <c r="J130" t="s">
+        <v>781</v>
+      </c>
+      <c r="K130" t="s">
+        <v>782</v>
+      </c>
+      <c r="L130" t="s">
         <v>783</v>
-      </c>
-      <c r="K130" t="s">
-        <v>784</v>
-      </c>
-      <c r="L130" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
@@ -8964,7 +8958,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C131">
         <v>2</v>
@@ -8979,22 +8973,22 @@
         <v>7412589630</v>
       </c>
       <c r="G131" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="H131" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="I131" t="b">
         <v>1</v>
       </c>
       <c r="J131" t="s">
+        <v>787</v>
+      </c>
+      <c r="K131" t="s">
+        <v>788</v>
+      </c>
+      <c r="L131" t="s">
         <v>789</v>
-      </c>
-      <c r="K131" t="s">
-        <v>790</v>
-      </c>
-      <c r="L131" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
@@ -9002,13 +8996,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C132">
         <v>3</v>
       </c>
       <c r="D132" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E132">
         <v>123456789012</v>
@@ -9017,22 +9011,22 @@
         <v>7890456123</v>
       </c>
       <c r="G132" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="H132" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="I132" t="b">
         <v>1</v>
       </c>
       <c r="J132" t="s">
+        <v>793</v>
+      </c>
+      <c r="K132" t="s">
+        <v>794</v>
+      </c>
+      <c r="L132" t="s">
         <v>795</v>
-      </c>
-      <c r="K132" t="s">
-        <v>796</v>
-      </c>
-      <c r="L132" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.2">
@@ -9040,13 +9034,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C133">
         <v>7</v>
       </c>
       <c r="D133" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E133">
         <v>123456789012</v>
@@ -9055,22 +9049,22 @@
         <v>7412589630</v>
       </c>
       <c r="G133" t="s">
+        <v>797</v>
+      </c>
+      <c r="H133" t="s">
+        <v>798</v>
+      </c>
+      <c r="I133" t="b">
+        <v>0</v>
+      </c>
+      <c r="J133" t="s">
         <v>799</v>
       </c>
-      <c r="H133" t="s">
+      <c r="K133" t="s">
         <v>800</v>
       </c>
-      <c r="I133" t="b">
-        <v>0</v>
-      </c>
-      <c r="J133" t="s">
+      <c r="L133" t="s">
         <v>801</v>
-      </c>
-      <c r="K133" t="s">
-        <v>802</v>
-      </c>
-      <c r="L133" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.2">
@@ -9078,13 +9072,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C134">
         <v>6</v>
       </c>
       <c r="D134" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E134">
         <v>345678901234</v>
@@ -9093,22 +9087,22 @@
         <v>7890456123</v>
       </c>
       <c r="G134" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="H134" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="I134" t="b">
         <v>1</v>
       </c>
       <c r="J134" t="s">
+        <v>805</v>
+      </c>
+      <c r="K134" t="s">
+        <v>806</v>
+      </c>
+      <c r="L134" t="s">
         <v>807</v>
-      </c>
-      <c r="K134" t="s">
-        <v>808</v>
-      </c>
-      <c r="L134" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.2">
@@ -9116,13 +9110,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C135">
         <v>5</v>
       </c>
       <c r="D135" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E135">
         <v>567890123456</v>
@@ -9131,22 +9125,22 @@
         <v>3214569870</v>
       </c>
       <c r="G135" t="s">
+        <v>809</v>
+      </c>
+      <c r="H135" t="s">
+        <v>810</v>
+      </c>
+      <c r="I135" t="b">
+        <v>0</v>
+      </c>
+      <c r="J135" t="s">
         <v>811</v>
       </c>
-      <c r="H135" t="s">
+      <c r="K135" t="s">
         <v>812</v>
       </c>
-      <c r="I135" t="b">
-        <v>0</v>
-      </c>
-      <c r="J135" t="s">
+      <c r="L135" t="s">
         <v>813</v>
-      </c>
-      <c r="K135" t="s">
-        <v>814</v>
-      </c>
-      <c r="L135" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.2">
@@ -9154,7 +9148,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C136">
         <v>9</v>
@@ -9169,22 +9163,22 @@
         <v>7412589630</v>
       </c>
       <c r="G136" t="s">
+        <v>815</v>
+      </c>
+      <c r="H136" t="s">
+        <v>816</v>
+      </c>
+      <c r="I136" t="b">
+        <v>0</v>
+      </c>
+      <c r="J136" t="s">
         <v>817</v>
       </c>
-      <c r="H136" t="s">
+      <c r="K136" t="s">
         <v>818</v>
       </c>
-      <c r="I136" t="b">
-        <v>0</v>
-      </c>
-      <c r="J136" t="s">
+      <c r="L136" t="s">
         <v>819</v>
-      </c>
-      <c r="K136" t="s">
-        <v>820</v>
-      </c>
-      <c r="L136" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.2">
@@ -9192,13 +9186,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C137">
         <v>6</v>
       </c>
       <c r="D137" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E137">
         <v>345678901234</v>
@@ -9207,22 +9201,22 @@
         <v>7412589630</v>
       </c>
       <c r="G137" t="s">
+        <v>821</v>
+      </c>
+      <c r="H137" t="s">
+        <v>822</v>
+      </c>
+      <c r="I137" t="b">
+        <v>0</v>
+      </c>
+      <c r="J137" t="s">
         <v>823</v>
       </c>
-      <c r="H137" t="s">
+      <c r="K137" t="s">
         <v>824</v>
       </c>
-      <c r="I137" t="b">
-        <v>0</v>
-      </c>
-      <c r="J137" t="s">
+      <c r="L137" t="s">
         <v>825</v>
-      </c>
-      <c r="K137" t="s">
-        <v>826</v>
-      </c>
-      <c r="L137" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.2">
@@ -9230,13 +9224,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C138">
         <v>8</v>
       </c>
       <c r="D138" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E138">
         <v>123456789012</v>
@@ -9245,22 +9239,22 @@
         <v>3214569870</v>
       </c>
       <c r="G138" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="H138" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="I138" t="b">
         <v>1</v>
       </c>
       <c r="J138" t="s">
+        <v>829</v>
+      </c>
+      <c r="K138" t="s">
+        <v>830</v>
+      </c>
+      <c r="L138" t="s">
         <v>831</v>
-      </c>
-      <c r="K138" t="s">
-        <v>832</v>
-      </c>
-      <c r="L138" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.2">
@@ -9268,13 +9262,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C139">
         <v>7</v>
       </c>
       <c r="D139" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E139">
         <v>123456789012</v>
@@ -9283,22 +9277,22 @@
         <v>3214569870</v>
       </c>
       <c r="G139" t="s">
+        <v>833</v>
+      </c>
+      <c r="H139" t="s">
+        <v>834</v>
+      </c>
+      <c r="I139" t="b">
+        <v>0</v>
+      </c>
+      <c r="J139" t="s">
         <v>835</v>
       </c>
-      <c r="H139" t="s">
+      <c r="K139" t="s">
         <v>836</v>
       </c>
-      <c r="I139" t="b">
-        <v>0</v>
-      </c>
-      <c r="J139" t="s">
+      <c r="L139" t="s">
         <v>837</v>
-      </c>
-      <c r="K139" t="s">
-        <v>838</v>
-      </c>
-      <c r="L139" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
@@ -9306,13 +9300,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C140">
         <v>9</v>
       </c>
       <c r="D140" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E140">
         <v>567890123456</v>
@@ -9321,22 +9315,22 @@
         <v>7890456123</v>
       </c>
       <c r="G140" t="s">
+        <v>839</v>
+      </c>
+      <c r="H140" t="s">
+        <v>840</v>
+      </c>
+      <c r="I140" t="b">
+        <v>0</v>
+      </c>
+      <c r="J140" t="s">
         <v>841</v>
       </c>
-      <c r="H140" t="s">
+      <c r="K140" t="s">
         <v>842</v>
       </c>
-      <c r="I140" t="b">
-        <v>0</v>
-      </c>
-      <c r="J140" t="s">
+      <c r="L140" t="s">
         <v>843</v>
-      </c>
-      <c r="K140" t="s">
-        <v>844</v>
-      </c>
-      <c r="L140" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
@@ -9344,13 +9338,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C141">
         <v>2</v>
       </c>
       <c r="D141" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E141">
         <v>345678901234</v>
@@ -9359,22 +9353,22 @@
         <v>7412589630</v>
       </c>
       <c r="G141" t="s">
+        <v>845</v>
+      </c>
+      <c r="H141" t="s">
+        <v>846</v>
+      </c>
+      <c r="I141" t="b">
+        <v>0</v>
+      </c>
+      <c r="J141" t="s">
         <v>847</v>
       </c>
-      <c r="H141" t="s">
+      <c r="K141" t="s">
         <v>848</v>
       </c>
-      <c r="I141" t="b">
-        <v>0</v>
-      </c>
-      <c r="J141" t="s">
+      <c r="L141" t="s">
         <v>849</v>
-      </c>
-      <c r="K141" t="s">
-        <v>850</v>
-      </c>
-      <c r="L141" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.2">
@@ -9382,7 +9376,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C142">
         <v>8</v>
@@ -9397,22 +9391,22 @@
         <v>7890456123</v>
       </c>
       <c r="G142" t="s">
+        <v>851</v>
+      </c>
+      <c r="H142" t="s">
+        <v>852</v>
+      </c>
+      <c r="I142" t="b">
+        <v>0</v>
+      </c>
+      <c r="J142" t="s">
         <v>853</v>
       </c>
-      <c r="H142" t="s">
+      <c r="K142" t="s">
         <v>854</v>
       </c>
-      <c r="I142" t="b">
-        <v>0</v>
-      </c>
-      <c r="J142" t="s">
+      <c r="L142" t="s">
         <v>855</v>
-      </c>
-      <c r="K142" t="s">
-        <v>856</v>
-      </c>
-      <c r="L142" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.2">
@@ -9420,13 +9414,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C143">
         <v>8</v>
       </c>
       <c r="D143" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E143">
         <v>345678901234</v>
@@ -9435,22 +9429,22 @@
         <v>7412589630</v>
       </c>
       <c r="G143" t="s">
+        <v>857</v>
+      </c>
+      <c r="H143" t="s">
+        <v>858</v>
+      </c>
+      <c r="I143" t="b">
+        <v>0</v>
+      </c>
+      <c r="J143" t="s">
         <v>859</v>
       </c>
-      <c r="H143" t="s">
+      <c r="K143" t="s">
         <v>860</v>
       </c>
-      <c r="I143" t="b">
-        <v>0</v>
-      </c>
-      <c r="J143" t="s">
+      <c r="L143" t="s">
         <v>861</v>
-      </c>
-      <c r="K143" t="s">
-        <v>862</v>
-      </c>
-      <c r="L143" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.2">
@@ -9458,13 +9452,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C144">
         <v>2</v>
       </c>
       <c r="D144" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E144">
         <v>123456789012</v>
@@ -9473,22 +9467,22 @@
         <v>7890456123</v>
       </c>
       <c r="G144" t="s">
+        <v>863</v>
+      </c>
+      <c r="H144" t="s">
+        <v>864</v>
+      </c>
+      <c r="I144" t="b">
+        <v>0</v>
+      </c>
+      <c r="J144" t="s">
         <v>865</v>
       </c>
-      <c r="H144" t="s">
+      <c r="K144" t="s">
         <v>866</v>
       </c>
-      <c r="I144" t="b">
-        <v>0</v>
-      </c>
-      <c r="J144" t="s">
+      <c r="L144" t="s">
         <v>867</v>
-      </c>
-      <c r="K144" t="s">
-        <v>868</v>
-      </c>
-      <c r="L144" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
@@ -9496,13 +9490,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C145">
         <v>5</v>
       </c>
       <c r="D145" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E145">
         <v>567890123456</v>
@@ -9511,22 +9505,22 @@
         <v>7890456123</v>
       </c>
       <c r="G145" t="s">
+        <v>869</v>
+      </c>
+      <c r="H145" t="s">
+        <v>870</v>
+      </c>
+      <c r="I145" t="b">
+        <v>0</v>
+      </c>
+      <c r="J145" t="s">
         <v>871</v>
       </c>
-      <c r="H145" t="s">
+      <c r="K145" t="s">
         <v>872</v>
       </c>
-      <c r="I145" t="b">
-        <v>0</v>
-      </c>
-      <c r="J145" t="s">
+      <c r="L145" t="s">
         <v>873</v>
-      </c>
-      <c r="K145" t="s">
-        <v>874</v>
-      </c>
-      <c r="L145" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
@@ -9534,13 +9528,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C146">
         <v>4</v>
       </c>
       <c r="D146" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E146">
         <v>345678901234</v>
@@ -9549,22 +9543,22 @@
         <v>7412589630</v>
       </c>
       <c r="G146" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="H146" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="I146" t="b">
         <v>1</v>
       </c>
       <c r="J146" t="s">
+        <v>877</v>
+      </c>
+      <c r="K146" t="s">
+        <v>878</v>
+      </c>
+      <c r="L146" t="s">
         <v>879</v>
-      </c>
-      <c r="K146" t="s">
-        <v>880</v>
-      </c>
-      <c r="L146" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
@@ -9572,13 +9566,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C147">
         <v>2</v>
       </c>
       <c r="D147" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E147">
         <v>345678901234</v>
@@ -9587,22 +9581,22 @@
         <v>7412589630</v>
       </c>
       <c r="G147" t="s">
+        <v>881</v>
+      </c>
+      <c r="H147" t="s">
+        <v>882</v>
+      </c>
+      <c r="I147" t="b">
+        <v>0</v>
+      </c>
+      <c r="J147" t="s">
         <v>883</v>
       </c>
-      <c r="H147" t="s">
+      <c r="K147" t="s">
         <v>884</v>
       </c>
-      <c r="I147" t="b">
-        <v>0</v>
-      </c>
-      <c r="J147" t="s">
+      <c r="L147" t="s">
         <v>885</v>
-      </c>
-      <c r="K147" t="s">
-        <v>886</v>
-      </c>
-      <c r="L147" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
@@ -9610,7 +9604,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C148">
         <v>6</v>
@@ -9625,22 +9619,22 @@
         <v>3214569870</v>
       </c>
       <c r="G148" t="s">
+        <v>887</v>
+      </c>
+      <c r="H148" t="s">
+        <v>888</v>
+      </c>
+      <c r="I148" t="b">
+        <v>0</v>
+      </c>
+      <c r="J148" t="s">
         <v>889</v>
       </c>
-      <c r="H148" t="s">
+      <c r="K148" t="s">
         <v>890</v>
       </c>
-      <c r="I148" t="b">
-        <v>0</v>
-      </c>
-      <c r="J148" t="s">
+      <c r="L148" t="s">
         <v>891</v>
-      </c>
-      <c r="K148" t="s">
-        <v>892</v>
-      </c>
-      <c r="L148" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
@@ -9648,13 +9642,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C149">
         <v>0</v>
       </c>
       <c r="D149" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E149">
         <v>345678901234</v>
@@ -9663,22 +9657,22 @@
         <v>3214569870</v>
       </c>
       <c r="G149" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="H149" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="I149" t="b">
         <v>1</v>
       </c>
       <c r="J149" t="s">
+        <v>895</v>
+      </c>
+      <c r="K149" t="s">
+        <v>896</v>
+      </c>
+      <c r="L149" t="s">
         <v>897</v>
-      </c>
-      <c r="K149" t="s">
-        <v>898</v>
-      </c>
-      <c r="L149" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
@@ -9686,13 +9680,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C150">
         <v>0</v>
       </c>
       <c r="D150" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E150">
         <v>345678901234</v>
@@ -9701,22 +9695,22 @@
         <v>7890456123</v>
       </c>
       <c r="G150" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="H150" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="I150" t="b">
         <v>1</v>
       </c>
       <c r="J150" t="s">
+        <v>901</v>
+      </c>
+      <c r="K150" t="s">
+        <v>902</v>
+      </c>
+      <c r="L150" t="s">
         <v>903</v>
-      </c>
-      <c r="K150" t="s">
-        <v>904</v>
-      </c>
-      <c r="L150" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
@@ -9724,7 +9718,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -9739,22 +9733,22 @@
         <v>7412589630</v>
       </c>
       <c r="G151" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="H151" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="I151" t="b">
         <v>1</v>
       </c>
       <c r="J151" t="s">
+        <v>907</v>
+      </c>
+      <c r="K151" t="s">
+        <v>908</v>
+      </c>
+      <c r="L151" t="s">
         <v>909</v>
-      </c>
-      <c r="K151" t="s">
-        <v>910</v>
-      </c>
-      <c r="L151" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
@@ -9762,7 +9756,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -9777,22 +9771,22 @@
         <v>7890456123</v>
       </c>
       <c r="G152" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="H152" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="I152" t="b">
         <v>1</v>
       </c>
       <c r="J152" t="s">
+        <v>913</v>
+      </c>
+      <c r="K152" t="s">
+        <v>914</v>
+      </c>
+      <c r="L152" t="s">
         <v>915</v>
-      </c>
-      <c r="K152" t="s">
-        <v>916</v>
-      </c>
-      <c r="L152" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
@@ -9800,13 +9794,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C153">
         <v>8</v>
       </c>
       <c r="D153" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E153">
         <v>567890123456</v>
@@ -9815,22 +9809,22 @@
         <v>7890456123</v>
       </c>
       <c r="G153" t="s">
+        <v>917</v>
+      </c>
+      <c r="H153" t="s">
+        <v>918</v>
+      </c>
+      <c r="I153" t="b">
+        <v>0</v>
+      </c>
+      <c r="J153" t="s">
         <v>919</v>
       </c>
-      <c r="H153" t="s">
+      <c r="K153" t="s">
         <v>920</v>
       </c>
-      <c r="I153" t="b">
-        <v>0</v>
-      </c>
-      <c r="J153" t="s">
+      <c r="L153" t="s">
         <v>921</v>
-      </c>
-      <c r="K153" t="s">
-        <v>922</v>
-      </c>
-      <c r="L153" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
@@ -9838,7 +9832,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C154">
         <v>7</v>
@@ -9853,22 +9847,22 @@
         <v>3214569870</v>
       </c>
       <c r="G154" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="H154" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="I154" t="b">
         <v>1</v>
       </c>
       <c r="J154" t="s">
+        <v>925</v>
+      </c>
+      <c r="K154" t="s">
+        <v>926</v>
+      </c>
+      <c r="L154" t="s">
         <v>927</v>
-      </c>
-      <c r="K154" t="s">
-        <v>928</v>
-      </c>
-      <c r="L154" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
@@ -9876,13 +9870,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C155">
         <v>0</v>
       </c>
       <c r="D155" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E155">
         <v>345678901234</v>
@@ -9891,22 +9885,22 @@
         <v>7412589630</v>
       </c>
       <c r="G155" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="H155" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="I155" t="b">
         <v>1</v>
       </c>
       <c r="J155" t="s">
+        <v>931</v>
+      </c>
+      <c r="K155" t="s">
+        <v>932</v>
+      </c>
+      <c r="L155" t="s">
         <v>933</v>
-      </c>
-      <c r="K155" t="s">
-        <v>934</v>
-      </c>
-      <c r="L155" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
@@ -9914,7 +9908,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="C156">
         <v>2</v>
@@ -9929,22 +9923,22 @@
         <v>7412589630</v>
       </c>
       <c r="G156" t="s">
+        <v>935</v>
+      </c>
+      <c r="H156" t="s">
+        <v>936</v>
+      </c>
+      <c r="I156" t="b">
+        <v>0</v>
+      </c>
+      <c r="J156" t="s">
         <v>937</v>
       </c>
-      <c r="H156" t="s">
+      <c r="K156" t="s">
         <v>938</v>
       </c>
-      <c r="I156" t="b">
-        <v>0</v>
-      </c>
-      <c r="J156" t="s">
+      <c r="L156" t="s">
         <v>939</v>
-      </c>
-      <c r="K156" t="s">
-        <v>940</v>
-      </c>
-      <c r="L156" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
@@ -9952,13 +9946,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C157">
         <v>5</v>
       </c>
       <c r="D157" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E157">
         <v>567890123456</v>
@@ -9967,22 +9961,22 @@
         <v>7890456123</v>
       </c>
       <c r="G157" t="s">
+        <v>941</v>
+      </c>
+      <c r="H157" t="s">
+        <v>942</v>
+      </c>
+      <c r="I157" t="b">
+        <v>0</v>
+      </c>
+      <c r="J157" t="s">
         <v>943</v>
       </c>
-      <c r="H157" t="s">
+      <c r="K157" t="s">
         <v>944</v>
       </c>
-      <c r="I157" t="b">
-        <v>0</v>
-      </c>
-      <c r="J157" t="s">
+      <c r="L157" t="s">
         <v>945</v>
-      </c>
-      <c r="K157" t="s">
-        <v>946</v>
-      </c>
-      <c r="L157" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
@@ -9990,13 +9984,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="C158">
         <v>3</v>
       </c>
       <c r="D158" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E158">
         <v>567890123456</v>
@@ -10005,22 +9999,22 @@
         <v>7890456123</v>
       </c>
       <c r="G158" t="s">
+        <v>947</v>
+      </c>
+      <c r="H158" t="s">
+        <v>948</v>
+      </c>
+      <c r="I158" t="b">
+        <v>0</v>
+      </c>
+      <c r="J158" t="s">
         <v>949</v>
       </c>
-      <c r="H158" t="s">
+      <c r="K158" t="s">
         <v>950</v>
       </c>
-      <c r="I158" t="b">
-        <v>0</v>
-      </c>
-      <c r="J158" t="s">
+      <c r="L158" t="s">
         <v>951</v>
-      </c>
-      <c r="K158" t="s">
-        <v>952</v>
-      </c>
-      <c r="L158" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
@@ -10028,7 +10022,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C159">
         <v>3</v>
@@ -10043,22 +10037,22 @@
         <v>7890456123</v>
       </c>
       <c r="G159" t="s">
+        <v>953</v>
+      </c>
+      <c r="H159" t="s">
+        <v>954</v>
+      </c>
+      <c r="I159" t="b">
+        <v>0</v>
+      </c>
+      <c r="J159" t="s">
         <v>955</v>
       </c>
-      <c r="H159" t="s">
+      <c r="K159" t="s">
         <v>956</v>
       </c>
-      <c r="I159" t="b">
-        <v>0</v>
-      </c>
-      <c r="J159" t="s">
+      <c r="L159" t="s">
         <v>957</v>
-      </c>
-      <c r="K159" t="s">
-        <v>958</v>
-      </c>
-      <c r="L159" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
@@ -10066,13 +10060,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C160">
         <v>4</v>
       </c>
       <c r="D160" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E160">
         <v>123456789012</v>
@@ -10081,22 +10075,22 @@
         <v>3214569870</v>
       </c>
       <c r="G160" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="H160" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="I160" t="b">
         <v>1</v>
       </c>
       <c r="J160" t="s">
+        <v>961</v>
+      </c>
+      <c r="K160" t="s">
+        <v>962</v>
+      </c>
+      <c r="L160" t="s">
         <v>963</v>
-      </c>
-      <c r="K160" t="s">
-        <v>964</v>
-      </c>
-      <c r="L160" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.2">
@@ -10104,7 +10098,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C161">
         <v>9</v>
@@ -10119,22 +10113,22 @@
         <v>7890456123</v>
       </c>
       <c r="G161" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="H161" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="I161" t="b">
         <v>1</v>
       </c>
       <c r="J161" t="s">
+        <v>967</v>
+      </c>
+      <c r="K161" t="s">
+        <v>968</v>
+      </c>
+      <c r="L161" t="s">
         <v>969</v>
-      </c>
-      <c r="K161" t="s">
-        <v>970</v>
-      </c>
-      <c r="L161" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.2">
@@ -10142,13 +10136,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C162">
         <v>3</v>
       </c>
       <c r="D162" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E162">
         <v>123456789012</v>
@@ -10157,22 +10151,22 @@
         <v>7890456123</v>
       </c>
       <c r="G162" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="H162" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="I162" t="b">
         <v>1</v>
       </c>
       <c r="J162" t="s">
+        <v>973</v>
+      </c>
+      <c r="K162" t="s">
+        <v>974</v>
+      </c>
+      <c r="L162" t="s">
         <v>975</v>
-      </c>
-      <c r="K162" t="s">
-        <v>976</v>
-      </c>
-      <c r="L162" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.2">
@@ -10180,7 +10174,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C163">
         <v>6</v>
@@ -10195,22 +10189,22 @@
         <v>3214569870</v>
       </c>
       <c r="G163" t="s">
+        <v>977</v>
+      </c>
+      <c r="H163" t="s">
+        <v>978</v>
+      </c>
+      <c r="I163" t="b">
+        <v>0</v>
+      </c>
+      <c r="J163" t="s">
         <v>979</v>
       </c>
-      <c r="H163" t="s">
+      <c r="K163" t="s">
         <v>980</v>
       </c>
-      <c r="I163" t="b">
-        <v>0</v>
-      </c>
-      <c r="J163" t="s">
+      <c r="L163" t="s">
         <v>981</v>
-      </c>
-      <c r="K163" t="s">
-        <v>982</v>
-      </c>
-      <c r="L163" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.2">
@@ -10218,7 +10212,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -10233,22 +10227,22 @@
         <v>3214569870</v>
       </c>
       <c r="G164" t="s">
+        <v>983</v>
+      </c>
+      <c r="H164" t="s">
+        <v>984</v>
+      </c>
+      <c r="I164" t="b">
+        <v>0</v>
+      </c>
+      <c r="J164" t="s">
         <v>985</v>
       </c>
-      <c r="H164" t="s">
+      <c r="K164" t="s">
         <v>986</v>
       </c>
-      <c r="I164" t="b">
-        <v>0</v>
-      </c>
-      <c r="J164" t="s">
+      <c r="L164" t="s">
         <v>987</v>
-      </c>
-      <c r="K164" t="s">
-        <v>988</v>
-      </c>
-      <c r="L164" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.2">
@@ -10256,7 +10250,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C165">
         <v>3</v>
@@ -10271,22 +10265,22 @@
         <v>3214569870</v>
       </c>
       <c r="G165" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="H165" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="I165" t="b">
         <v>1</v>
       </c>
       <c r="J165" t="s">
+        <v>991</v>
+      </c>
+      <c r="K165" t="s">
+        <v>992</v>
+      </c>
+      <c r="L165" t="s">
         <v>993</v>
-      </c>
-      <c r="K165" t="s">
-        <v>994</v>
-      </c>
-      <c r="L165" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.2">
@@ -10294,7 +10288,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C166">
         <v>4</v>
@@ -10309,22 +10303,22 @@
         <v>7890456123</v>
       </c>
       <c r="G166" t="s">
+        <v>995</v>
+      </c>
+      <c r="H166" t="s">
+        <v>996</v>
+      </c>
+      <c r="I166" t="b">
+        <v>0</v>
+      </c>
+      <c r="J166" t="s">
         <v>997</v>
       </c>
-      <c r="H166" t="s">
+      <c r="K166" t="s">
         <v>998</v>
       </c>
-      <c r="I166" t="b">
-        <v>0</v>
-      </c>
-      <c r="J166" t="s">
+      <c r="L166" t="s">
         <v>999</v>
-      </c>
-      <c r="K166" t="s">
-        <v>1000</v>
-      </c>
-      <c r="L166" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.2">
@@ -10332,13 +10326,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C167">
         <v>5</v>
       </c>
       <c r="D167" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E167">
         <v>567890123456</v>
@@ -10347,22 +10341,22 @@
         <v>3214569870</v>
       </c>
       <c r="G167" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H167" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I167" t="b">
+        <v>0</v>
+      </c>
+      <c r="J167" t="s">
         <v>1003</v>
       </c>
-      <c r="H167" t="s">
+      <c r="K167" t="s">
         <v>1004</v>
       </c>
-      <c r="I167" t="b">
-        <v>0</v>
-      </c>
-      <c r="J167" t="s">
+      <c r="L167" t="s">
         <v>1005</v>
-      </c>
-      <c r="K167" t="s">
-        <v>1006</v>
-      </c>
-      <c r="L167" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.2">
@@ -10370,13 +10364,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C168">
         <v>6</v>
       </c>
       <c r="D168" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E168">
         <v>123456789012</v>
@@ -10385,22 +10379,22 @@
         <v>7412589630</v>
       </c>
       <c r="G168" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H168" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I168" t="b">
+        <v>0</v>
+      </c>
+      <c r="J168" t="s">
         <v>1009</v>
       </c>
-      <c r="H168" t="s">
+      <c r="K168" t="s">
         <v>1010</v>
       </c>
-      <c r="I168" t="b">
-        <v>0</v>
-      </c>
-      <c r="J168" t="s">
+      <c r="L168" t="s">
         <v>1011</v>
-      </c>
-      <c r="K168" t="s">
-        <v>1012</v>
-      </c>
-      <c r="L168" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.2">
@@ -10408,13 +10402,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C169">
         <v>0</v>
       </c>
       <c r="D169" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E169">
         <v>123456789012</v>
@@ -10423,22 +10417,22 @@
         <v>3214569870</v>
       </c>
       <c r="G169" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H169" t="s">
+        <v>1014</v>
+      </c>
+      <c r="I169" t="b">
+        <v>0</v>
+      </c>
+      <c r="J169" t="s">
         <v>1015</v>
       </c>
-      <c r="H169" t="s">
+      <c r="K169" t="s">
         <v>1016</v>
       </c>
-      <c r="I169" t="b">
-        <v>0</v>
-      </c>
-      <c r="J169" t="s">
+      <c r="L169" t="s">
         <v>1017</v>
-      </c>
-      <c r="K169" t="s">
-        <v>1018</v>
-      </c>
-      <c r="L169" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.2">
@@ -10446,13 +10440,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C170">
         <v>6</v>
       </c>
       <c r="D170" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E170">
         <v>123456789012</v>
@@ -10461,22 +10455,22 @@
         <v>7890456123</v>
       </c>
       <c r="G170" t="s">
+        <v>1019</v>
+      </c>
+      <c r="H170" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I170" t="b">
+        <v>0</v>
+      </c>
+      <c r="J170" t="s">
         <v>1021</v>
       </c>
-      <c r="H170" t="s">
+      <c r="K170" t="s">
         <v>1022</v>
       </c>
-      <c r="I170" t="b">
-        <v>0</v>
-      </c>
-      <c r="J170" t="s">
+      <c r="L170" t="s">
         <v>1023</v>
-      </c>
-      <c r="K170" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L170" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.2">
@@ -10484,13 +10478,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C171">
         <v>5</v>
       </c>
       <c r="D171" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E171">
         <v>345678901234</v>
@@ -10499,22 +10493,22 @@
         <v>3214569870</v>
       </c>
       <c r="G171" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="H171" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="I171" t="b">
         <v>1</v>
       </c>
       <c r="J171" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K171" t="s">
+        <v>1028</v>
+      </c>
+      <c r="L171" t="s">
         <v>1029</v>
-      </c>
-      <c r="K171" t="s">
-        <v>1030</v>
-      </c>
-      <c r="L171" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.2">
@@ -10522,7 +10516,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C172">
         <v>4</v>
@@ -10537,22 +10531,22 @@
         <v>7412589630</v>
       </c>
       <c r="G172" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="H172" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="I172" t="b">
         <v>1</v>
       </c>
       <c r="J172" t="s">
+        <v>1033</v>
+      </c>
+      <c r="K172" t="s">
+        <v>1034</v>
+      </c>
+      <c r="L172" t="s">
         <v>1035</v>
-      </c>
-      <c r="K172" t="s">
-        <v>1036</v>
-      </c>
-      <c r="L172" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.2">
@@ -10560,13 +10554,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C173">
         <v>1</v>
       </c>
       <c r="D173" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E173">
         <v>567890123456</v>
@@ -10575,22 +10569,22 @@
         <v>3214569870</v>
       </c>
       <c r="G173" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H173" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I173" t="b">
+        <v>0</v>
+      </c>
+      <c r="J173" t="s">
         <v>1039</v>
       </c>
-      <c r="H173" t="s">
+      <c r="K173" t="s">
         <v>1040</v>
       </c>
-      <c r="I173" t="b">
-        <v>0</v>
-      </c>
-      <c r="J173" t="s">
+      <c r="L173" t="s">
         <v>1041</v>
-      </c>
-      <c r="K173" t="s">
-        <v>1042</v>
-      </c>
-      <c r="L173" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.2">
@@ -10598,7 +10592,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C174">
         <v>8</v>
@@ -10613,22 +10607,22 @@
         <v>3214569870</v>
       </c>
       <c r="G174" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H174" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I174" t="b">
+        <v>0</v>
+      </c>
+      <c r="J174" t="s">
         <v>1045</v>
       </c>
-      <c r="H174" t="s">
+      <c r="K174" t="s">
         <v>1046</v>
       </c>
-      <c r="I174" t="b">
-        <v>0</v>
-      </c>
-      <c r="J174" t="s">
+      <c r="L174" t="s">
         <v>1047</v>
-      </c>
-      <c r="K174" t="s">
-        <v>1048</v>
-      </c>
-      <c r="L174" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.2">
@@ -10636,13 +10630,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C175">
         <v>7</v>
       </c>
       <c r="D175" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E175">
         <v>123456789012</v>
@@ -10651,22 +10645,22 @@
         <v>3214569870</v>
       </c>
       <c r="G175" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="H175" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="I175" t="b">
         <v>1</v>
       </c>
       <c r="J175" t="s">
+        <v>1051</v>
+      </c>
+      <c r="K175" t="s">
+        <v>1052</v>
+      </c>
+      <c r="L175" t="s">
         <v>1053</v>
-      </c>
-      <c r="K175" t="s">
-        <v>1054</v>
-      </c>
-      <c r="L175" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.2">
@@ -10674,7 +10668,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C176">
         <v>3</v>
@@ -10689,22 +10683,22 @@
         <v>7412589630</v>
       </c>
       <c r="G176" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="H176" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="I176" t="b">
         <v>1</v>
       </c>
       <c r="J176" t="s">
+        <v>1057</v>
+      </c>
+      <c r="K176" t="s">
+        <v>1058</v>
+      </c>
+      <c r="L176" t="s">
         <v>1059</v>
-      </c>
-      <c r="K176" t="s">
-        <v>1060</v>
-      </c>
-      <c r="L176" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.2">
@@ -10712,13 +10706,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C177">
         <v>4</v>
       </c>
       <c r="D177" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E177">
         <v>567890123456</v>
@@ -10727,22 +10721,22 @@
         <v>3214569870</v>
       </c>
       <c r="G177" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H177" t="s">
+        <v>1062</v>
+      </c>
+      <c r="I177" t="b">
+        <v>0</v>
+      </c>
+      <c r="J177" t="s">
         <v>1063</v>
       </c>
-      <c r="H177" t="s">
+      <c r="K177" t="s">
         <v>1064</v>
       </c>
-      <c r="I177" t="b">
-        <v>0</v>
-      </c>
-      <c r="J177" t="s">
+      <c r="L177" t="s">
         <v>1065</v>
-      </c>
-      <c r="K177" t="s">
-        <v>1066</v>
-      </c>
-      <c r="L177" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.2">
@@ -10750,13 +10744,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C178">
         <v>4</v>
       </c>
       <c r="D178" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E178">
         <v>345678901234</v>
@@ -10765,22 +10759,22 @@
         <v>3214569870</v>
       </c>
       <c r="G178" t="s">
+        <v>1067</v>
+      </c>
+      <c r="H178" t="s">
+        <v>1068</v>
+      </c>
+      <c r="I178" t="b">
+        <v>0</v>
+      </c>
+      <c r="J178" t="s">
         <v>1069</v>
       </c>
-      <c r="H178" t="s">
+      <c r="K178" t="s">
         <v>1070</v>
       </c>
-      <c r="I178" t="b">
-        <v>0</v>
-      </c>
-      <c r="J178" t="s">
+      <c r="L178" t="s">
         <v>1071</v>
-      </c>
-      <c r="K178" t="s">
-        <v>1072</v>
-      </c>
-      <c r="L178" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.2">
@@ -10788,13 +10782,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C179">
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E179">
         <v>567890123456</v>
@@ -10803,22 +10797,22 @@
         <v>7890456123</v>
       </c>
       <c r="G179" t="s">
+        <v>1073</v>
+      </c>
+      <c r="H179" t="s">
+        <v>1074</v>
+      </c>
+      <c r="I179" t="b">
+        <v>0</v>
+      </c>
+      <c r="J179" t="s">
         <v>1075</v>
       </c>
-      <c r="H179" t="s">
+      <c r="K179" t="s">
         <v>1076</v>
       </c>
-      <c r="I179" t="b">
-        <v>0</v>
-      </c>
-      <c r="J179" t="s">
+      <c r="L179" t="s">
         <v>1077</v>
-      </c>
-      <c r="K179" t="s">
-        <v>1078</v>
-      </c>
-      <c r="L179" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.2">
@@ -10826,13 +10820,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C180">
         <v>0</v>
       </c>
       <c r="D180" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E180">
         <v>567890123456</v>
@@ -10841,22 +10835,22 @@
         <v>7412589630</v>
       </c>
       <c r="G180" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H180" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I180" t="b">
+        <v>0</v>
+      </c>
+      <c r="J180" t="s">
         <v>1081</v>
       </c>
-      <c r="H180" t="s">
+      <c r="K180" t="s">
         <v>1082</v>
       </c>
-      <c r="I180" t="b">
-        <v>0</v>
-      </c>
-      <c r="J180" t="s">
+      <c r="L180" t="s">
         <v>1083</v>
-      </c>
-      <c r="K180" t="s">
-        <v>1084</v>
-      </c>
-      <c r="L180" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.2">
@@ -10864,13 +10858,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C181">
         <v>4</v>
       </c>
       <c r="D181" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E181">
         <v>567890123456</v>
@@ -10879,22 +10873,22 @@
         <v>7412589630</v>
       </c>
       <c r="G181" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H181" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="I181" t="b">
         <v>1</v>
       </c>
       <c r="J181" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K181" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L181" t="s">
         <v>1089</v>
-      </c>
-      <c r="K181" t="s">
-        <v>1090</v>
-      </c>
-      <c r="L181" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.2">
@@ -10902,13 +10896,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="C182">
         <v>5</v>
       </c>
       <c r="D182" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E182">
         <v>567890123456</v>
@@ -10917,22 +10911,22 @@
         <v>7890456123</v>
       </c>
       <c r="G182" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H182" t="s">
+        <v>1092</v>
+      </c>
+      <c r="I182" t="b">
+        <v>0</v>
+      </c>
+      <c r="J182" t="s">
         <v>1093</v>
       </c>
-      <c r="H182" t="s">
+      <c r="K182" t="s">
         <v>1094</v>
       </c>
-      <c r="I182" t="b">
-        <v>0</v>
-      </c>
-      <c r="J182" t="s">
+      <c r="L182" t="s">
         <v>1095</v>
-      </c>
-      <c r="K182" t="s">
-        <v>1096</v>
-      </c>
-      <c r="L182" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.2">
@@ -10940,13 +10934,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="C183">
         <v>3</v>
       </c>
       <c r="D183" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E183">
         <v>123456789012</v>
@@ -10955,22 +10949,22 @@
         <v>3214569870</v>
       </c>
       <c r="G183" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="H183" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="I183" t="b">
         <v>1</v>
       </c>
       <c r="J183" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K183" t="s">
+        <v>1100</v>
+      </c>
+      <c r="L183" t="s">
         <v>1101</v>
-      </c>
-      <c r="K183" t="s">
-        <v>1102</v>
-      </c>
-      <c r="L183" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.2">
@@ -10978,13 +10972,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="C184">
         <v>6</v>
       </c>
       <c r="D184" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E184">
         <v>567890123456</v>
@@ -10993,22 +10987,22 @@
         <v>7412589630</v>
       </c>
       <c r="G184" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="H184" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="I184" t="b">
         <v>1</v>
       </c>
       <c r="J184" t="s">
+        <v>1105</v>
+      </c>
+      <c r="K184" t="s">
+        <v>1106</v>
+      </c>
+      <c r="L184" t="s">
         <v>1107</v>
-      </c>
-      <c r="K184" t="s">
-        <v>1108</v>
-      </c>
-      <c r="L184" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.2">
@@ -11016,13 +11010,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="C185">
         <v>0</v>
       </c>
       <c r="D185" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E185">
         <v>567890123456</v>
@@ -11031,22 +11025,22 @@
         <v>3214569870</v>
       </c>
       <c r="G185" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="H185" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="I185" t="b">
         <v>1</v>
       </c>
       <c r="J185" t="s">
+        <v>1111</v>
+      </c>
+      <c r="K185" t="s">
+        <v>1112</v>
+      </c>
+      <c r="L185" t="s">
         <v>1113</v>
-      </c>
-      <c r="K185" t="s">
-        <v>1114</v>
-      </c>
-      <c r="L185" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.2">
@@ -11054,13 +11048,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="C186">
         <v>3</v>
       </c>
       <c r="D186" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E186">
         <v>567890123456</v>
@@ -11069,22 +11063,22 @@
         <v>3214569870</v>
       </c>
       <c r="G186" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H186" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="I186" t="b">
         <v>1</v>
       </c>
       <c r="J186" t="s">
+        <v>1117</v>
+      </c>
+      <c r="K186" t="s">
+        <v>1118</v>
+      </c>
+      <c r="L186" t="s">
         <v>1119</v>
-      </c>
-      <c r="K186" t="s">
-        <v>1120</v>
-      </c>
-      <c r="L186" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.2">
@@ -11092,13 +11086,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="C187">
         <v>2</v>
       </c>
       <c r="D187" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E187">
         <v>123456789012</v>
@@ -11107,22 +11101,22 @@
         <v>7890456123</v>
       </c>
       <c r="G187" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H187" t="s">
+        <v>1122</v>
+      </c>
+      <c r="I187" t="b">
+        <v>0</v>
+      </c>
+      <c r="J187" t="s">
         <v>1123</v>
       </c>
-      <c r="H187" t="s">
+      <c r="K187" t="s">
         <v>1124</v>
       </c>
-      <c r="I187" t="b">
-        <v>0</v>
-      </c>
-      <c r="J187" t="s">
+      <c r="L187" t="s">
         <v>1125</v>
-      </c>
-      <c r="K187" t="s">
-        <v>1126</v>
-      </c>
-      <c r="L187" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.2">
@@ -11130,7 +11124,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="C188">
         <v>7</v>
@@ -11145,22 +11139,22 @@
         <v>7412589630</v>
       </c>
       <c r="G188" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="H188" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="I188" t="b">
         <v>1</v>
       </c>
       <c r="J188" t="s">
+        <v>1129</v>
+      </c>
+      <c r="K188" t="s">
+        <v>1130</v>
+      </c>
+      <c r="L188" t="s">
         <v>1131</v>
-      </c>
-      <c r="K188" t="s">
-        <v>1132</v>
-      </c>
-      <c r="L188" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.2">
@@ -11168,13 +11162,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="C189">
         <v>3</v>
       </c>
       <c r="D189" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E189">
         <v>345678901234</v>
@@ -11183,22 +11177,22 @@
         <v>7890456123</v>
       </c>
       <c r="G189" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H189" t="s">
+        <v>1134</v>
+      </c>
+      <c r="I189" t="b">
+        <v>0</v>
+      </c>
+      <c r="J189" t="s">
         <v>1135</v>
       </c>
-      <c r="H189" t="s">
+      <c r="K189" t="s">
         <v>1136</v>
       </c>
-      <c r="I189" t="b">
-        <v>0</v>
-      </c>
-      <c r="J189" t="s">
+      <c r="L189" t="s">
         <v>1137</v>
-      </c>
-      <c r="K189" t="s">
-        <v>1138</v>
-      </c>
-      <c r="L189" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.2">
@@ -11206,13 +11200,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="C190">
         <v>6</v>
       </c>
       <c r="D190" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E190">
         <v>567890123456</v>
@@ -11221,22 +11215,22 @@
         <v>3214569870</v>
       </c>
       <c r="G190" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="H190" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="I190" t="b">
         <v>1</v>
       </c>
       <c r="J190" t="s">
+        <v>1141</v>
+      </c>
+      <c r="K190" t="s">
+        <v>1142</v>
+      </c>
+      <c r="L190" t="s">
         <v>1143</v>
-      </c>
-      <c r="K190" t="s">
-        <v>1144</v>
-      </c>
-      <c r="L190" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.2">
@@ -11244,7 +11238,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -11259,22 +11253,22 @@
         <v>7412589630</v>
       </c>
       <c r="G191" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="H191" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="I191" t="b">
         <v>1</v>
       </c>
       <c r="J191" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K191" t="s">
+        <v>1148</v>
+      </c>
+      <c r="L191" t="s">
         <v>1149</v>
-      </c>
-      <c r="K191" t="s">
-        <v>1150</v>
-      </c>
-      <c r="L191" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.2">
@@ -11282,13 +11276,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C192">
         <v>1</v>
       </c>
       <c r="D192" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E192">
         <v>567890123456</v>
@@ -11297,22 +11291,22 @@
         <v>7890456123</v>
       </c>
       <c r="G192" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="H192" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="I192" t="b">
         <v>1</v>
       </c>
       <c r="J192" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K192" t="s">
+        <v>1153</v>
+      </c>
+      <c r="L192" t="s">
         <v>1154</v>
-      </c>
-      <c r="K192" t="s">
-        <v>1155</v>
-      </c>
-      <c r="L192" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.2">
@@ -11320,7 +11314,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="C193">
         <v>5</v>
@@ -11335,22 +11329,22 @@
         <v>7890456123</v>
       </c>
       <c r="G193" t="s">
+        <v>1156</v>
+      </c>
+      <c r="H193" t="s">
+        <v>1157</v>
+      </c>
+      <c r="I193" t="b">
+        <v>0</v>
+      </c>
+      <c r="J193" t="s">
         <v>1158</v>
       </c>
-      <c r="H193" t="s">
+      <c r="K193" t="s">
         <v>1159</v>
       </c>
-      <c r="I193" t="b">
-        <v>0</v>
-      </c>
-      <c r="J193" t="s">
+      <c r="L193" t="s">
         <v>1160</v>
-      </c>
-      <c r="K193" t="s">
-        <v>1161</v>
-      </c>
-      <c r="L193" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.2">
@@ -11358,13 +11352,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C194">
         <v>4</v>
       </c>
       <c r="D194" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E194">
         <v>345678901234</v>
@@ -11373,22 +11367,22 @@
         <v>7412589630</v>
       </c>
       <c r="G194" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="H194" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="I194" t="b">
         <v>1</v>
       </c>
       <c r="J194" t="s">
+        <v>1164</v>
+      </c>
+      <c r="K194" t="s">
+        <v>1165</v>
+      </c>
+      <c r="L194" t="s">
         <v>1166</v>
-      </c>
-      <c r="K194" t="s">
-        <v>1167</v>
-      </c>
-      <c r="L194" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.2">
@@ -11396,7 +11390,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -11411,22 +11405,22 @@
         <v>3214569870</v>
       </c>
       <c r="G195" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H195" t="s">
+        <v>1169</v>
+      </c>
+      <c r="I195" t="b">
+        <v>0</v>
+      </c>
+      <c r="J195" t="s">
         <v>1170</v>
       </c>
-      <c r="H195" t="s">
+      <c r="K195" t="s">
         <v>1171</v>
       </c>
-      <c r="I195" t="b">
-        <v>0</v>
-      </c>
-      <c r="J195" t="s">
+      <c r="L195" t="s">
         <v>1172</v>
-      </c>
-      <c r="K195" t="s">
-        <v>1173</v>
-      </c>
-      <c r="L195" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.2">
@@ -11434,13 +11428,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C196">
         <v>1</v>
       </c>
       <c r="D196" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E196">
         <v>123456789012</v>
@@ -11449,22 +11443,22 @@
         <v>7890456123</v>
       </c>
       <c r="G196" t="s">
+        <v>1174</v>
+      </c>
+      <c r="H196" t="s">
+        <v>1175</v>
+      </c>
+      <c r="I196" t="b">
+        <v>0</v>
+      </c>
+      <c r="J196" t="s">
         <v>1176</v>
       </c>
-      <c r="H196" t="s">
+      <c r="K196" t="s">
         <v>1177</v>
       </c>
-      <c r="I196" t="b">
-        <v>0</v>
-      </c>
-      <c r="J196" t="s">
+      <c r="L196" t="s">
         <v>1178</v>
-      </c>
-      <c r="K196" t="s">
-        <v>1179</v>
-      </c>
-      <c r="L196" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.2">
@@ -11472,13 +11466,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="C197">
         <v>5</v>
       </c>
       <c r="D197" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E197">
         <v>567890123456</v>
@@ -11487,22 +11481,22 @@
         <v>3214569870</v>
       </c>
       <c r="G197" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H197" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I197" t="b">
+        <v>0</v>
+      </c>
+      <c r="J197" t="s">
         <v>1182</v>
       </c>
-      <c r="H197" t="s">
+      <c r="K197" t="s">
         <v>1183</v>
       </c>
-      <c r="I197" t="b">
-        <v>0</v>
-      </c>
-      <c r="J197" t="s">
+      <c r="L197" t="s">
         <v>1184</v>
-      </c>
-      <c r="K197" t="s">
-        <v>1185</v>
-      </c>
-      <c r="L197" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.2">
@@ -11510,7 +11504,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C198">
         <v>6</v>
@@ -11525,22 +11519,22 @@
         <v>3214569870</v>
       </c>
       <c r="G198" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="H198" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="I198" t="b">
         <v>1</v>
       </c>
       <c r="J198" t="s">
+        <v>1188</v>
+      </c>
+      <c r="K198" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L198" t="s">
         <v>1190</v>
-      </c>
-      <c r="K198" t="s">
-        <v>1191</v>
-      </c>
-      <c r="L198" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.2">
@@ -11548,13 +11542,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C199">
         <v>8</v>
       </c>
       <c r="D199" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E199">
         <v>567890123456</v>
@@ -11563,22 +11557,22 @@
         <v>7890456123</v>
       </c>
       <c r="G199" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="H199" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="I199" t="b">
         <v>1</v>
       </c>
       <c r="J199" t="s">
+        <v>1194</v>
+      </c>
+      <c r="K199" t="s">
+        <v>1195</v>
+      </c>
+      <c r="L199" t="s">
         <v>1196</v>
-      </c>
-      <c r="K199" t="s">
-        <v>1197</v>
-      </c>
-      <c r="L199" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.2">
@@ -11586,13 +11580,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="C200">
         <v>5</v>
       </c>
       <c r="D200" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E200">
         <v>345678901234</v>
@@ -11601,22 +11595,22 @@
         <v>7890456123</v>
       </c>
       <c r="G200" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="H200" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="I200" t="b">
         <v>1</v>
       </c>
       <c r="J200" t="s">
+        <v>1200</v>
+      </c>
+      <c r="K200" t="s">
+        <v>1201</v>
+      </c>
+      <c r="L200" t="s">
         <v>1202</v>
-      </c>
-      <c r="K200" t="s">
-        <v>1203</v>
-      </c>
-      <c r="L200" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.2">
@@ -11624,7 +11618,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="C201">
         <v>4</v>
@@ -11639,22 +11633,22 @@
         <v>3214569870</v>
       </c>
       <c r="G201" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="H201" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="I201" t="b">
         <v>1</v>
       </c>
       <c r="J201" t="s">
+        <v>1206</v>
+      </c>
+      <c r="K201" t="s">
+        <v>1207</v>
+      </c>
+      <c r="L201" t="s">
         <v>1208</v>
-      </c>
-      <c r="K201" t="s">
-        <v>1209</v>
-      </c>
-      <c r="L201" t="s">
-        <v>1210</v>
       </c>
     </row>
   </sheetData>
